--- a/Aspire_Combined_Underwriting_Model_v5_SAMPLE.xlsx
+++ b/Aspire_Combined_Underwriting_Model_v5_SAMPLE.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="573">
   <si>
     <t xml:space="preserve"> UNDERWRITING TOOL</t>
   </si>
@@ -325,88 +325,49 @@
     <t xml:space="preserve">MAX FUND at the sizing line</t>
   </si>
   <si>
-    <t xml:space="preserve">F.  FINAL OFFER  (PLANNED - outline only)   =   max at the sizing line (section E)  -&gt;  house-book outcome applied</t>
+    <t xml:space="preserve">F.  FINAL OFFER   =   max at the sizing line (section E)   +   house-book outcome</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
   </si>
   <si>
-    <t xml:space="preserve">How it will be computed</t>
+    <t xml:space="preserve">Detail</t>
   </si>
   <si>
     <t xml:space="preserve">FINAL DECISION</t>
   </si>
   <si>
-    <t xml:space="preserve">APPROVE / CONDITIONAL / DECLINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; DECLINE if D says DECLINE on the merchant side (knockout, red flags, below minimum). CONDITIONAL if any metric is YELLOW at the final offer or the house-book outcome is Negative. Else APPROVE.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recommended fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; Section E max fund (C73). If the house-book outcome is Negative: C73 x (1 - fund cut % on Controls). Floor to $500. Never above C73.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40 / 1.45 / 1.49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; Band factor D72 (unchanged by history for now).</t>
+    <t xml:space="preserve">Green-line max fund (cash flow only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max fund at the sizing line (C73)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECOMMENDED FUND</t>
   </si>
   <si>
     <t xml:space="preserve">Term</t>
   </si>
   <si>
-    <t xml:space="preserve">weeks or daily pmts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; Band term C72; shown in the frequency of E6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">per week / per day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; fund x factor / term (daily); x5 for weekly.</t>
+    <t xml:space="preserve">Daily-equivalent payment</t>
   </si>
   <si>
     <t xml:space="preserve">Holdback % at final offer</t>
   </si>
   <si>
-    <t xml:space="preserve">%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; payment x 21.655 / avg revenue, with GREEN / YELLOW status against Controls. Yellow is allowed only when the outcome is Supportive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total LVG / daily debt-balance / fund-rev at final offer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; same re-check for the other three offer-side metrics; RED must be impossible because the sizing line stops short of the red line.</t>
+    <t xml:space="preserve">Total LVG at final offer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily debt / balance at final offer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fund / revenue at final offer</t>
   </si>
   <si>
     <t xml:space="preserve">House-book outcome</t>
   </si>
   <si>
-    <t xml:space="preserve">Supportive / Neutral / Negative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; from Historical Score C35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primary cohort and its numbers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-&gt; tier, seasoned n, PLR, ROF, index - from Historical Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layer 1 stays the ceiling: the sizing line never reaches the red line, knockouts are never removed, the final fund never exceeds C73.</t>
+    <t xml:space="preserve">Supportive history raises C73 above the green-line max (row 78) by moving the sizing lines; negative history cuts it. Knockouts are never removed and no metric may be red at the final offer.</t>
   </si>
   <si>
     <t xml:space="preserve">HISTORICAL SCORE  </t>
@@ -1793,7 +1754,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
@@ -1809,10 +1770,11 @@
     <numFmt numFmtId="176" formatCode="#,##0"/>
     <numFmt numFmtId="177" formatCode="General"/>
     <numFmt numFmtId="178" formatCode="\$#,##0"/>
-    <numFmt numFmtId="179" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="180" formatCode="0.0000"/>
+    <numFmt numFmtId="179" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="180" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="181" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1945,9 +1907,8 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF374151"/>
+      <b val="true"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1956,13 +1917,6 @@
       <b val="true"/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2172,7 +2126,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="146">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2533,36 +2487,68 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2585,7 +2571,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2593,15 +2579,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2609,7 +2591,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2621,7 +2603,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2681,7 +2663,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="180" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="181" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2697,7 +2679,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="179" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="180" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2738,7 +2720,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="1"/>
@@ -2780,6 +2762,39 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFF97316"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4435,7 +4450,7 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="6" t="s">
         <v>98</v>
       </c>
@@ -4446,7 +4461,7 @@
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="89" t="s">
         <v>99</v>
       </c>
@@ -4461,155 +4476,221 @@
       <c r="G76" s="89"/>
       <c r="H76" s="89"/>
     </row>
-    <row r="77" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B77" s="55" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="C77" s="90" t="s">
+      <c r="C77" s="91" t="str">
+        <f aca="false">IF(C24=0,"",IF(OR(C73="-",C73="",C80="",C80=0,C80&lt;E61,COUNTIF(F42:F45,"RED")+COUNTIF(F42:F45,"KNOCKOUT")+COUNTIF(D85:D88,"RED")&gt;=C61),"DECLINE",IF(OR(COUNTIF(D85:D88,"YELLOW")&gt;0,COUNTIF(F42:F45,"YELLOW")&gt;0,C89="Negative"),"CONDITIONAL","APPROVE")))</f>
+        <v>CONDITIONAL</v>
+      </c>
+      <c r="D77" s="92" t="str">
+        <f aca="false">IF(C77="","Enter bank data.",IF(C77="DECLINE",IF(C73="-","Merchant knockout: "&amp;INDEX(B42:B45,MATCH("KNOCKOUT",F42:F45,0)),IF(OR(C73="",C80=0),"No clean room under the sizing line.",IF(C80&lt;E61,"Fund "&amp;TEXT(C80,"$#,##0")&amp;" is below the minimum "&amp;TEXT(E61,"$#,##0"),"Red flags reached the limit."))),IF(C77="APPROVE","All metrics green at the final offer; house book neutral or supportive.","Yellows at the final offer, or the house book is negative.")))</f>
+        <v>Yellows at the final offer, or the house book is negative.</v>
+      </c>
+      <c r="E77" s="92"/>
+      <c r="F77" s="92"/>
+      <c r="G77" s="92"/>
+      <c r="H77" s="92"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="D77" s="91" t="s">
+      <c r="C78" s="93" t="n">
+        <f aca="false">IF(C24=0,"",IF(COUNTIF(F42:F45,"KNOCKOUT")&gt;0,"-",IF(MAX(0,MIN(D39*C24/$K$9,(D38*C24-F34)/$K$9,IF(D24=0,0,D40*D24-E34)))=0,0,FLOOR(MAX(0,MIN(D39*C24/$K$9,(D38*C24-F34)/$K$9,IF(D24=0,0,D40*D24-E34)))*MAX(20,MIN(INDEX(Controls!$B$5:$B$8,MATCH(IF(SUMPRODUCT(--(F38:F45&lt;&gt;""))=0,0,C65*7/SUMPRODUCT(--(F38:F45&lt;&gt;""))),Controls!$A$5:$A$8,1)),FLOOR(Controls!$B$9*$K$9,5),FLOOR(D41*C24*D72/MAX(0,MIN(D39*C24/$K$9,(D38*C24-F34)/$K$9,IF(D24=0,0,D40*D24-E34))),5)))/D72,500))))</f>
+        <v>51000</v>
+      </c>
+      <c r="D78" s="92" t="str">
+        <f aca="false">"what the tool as built would size, with no history"</f>
+        <v>what the tool as built would size, with no history</v>
+      </c>
+      <c r="E78" s="92"/>
+      <c r="F78" s="92"/>
+      <c r="G78" s="92"/>
+      <c r="H78" s="92"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="90" t="s">
         <v>103</v>
       </c>
-      <c r="E77" s="91"/>
-      <c r="F77" s="91"/>
-      <c r="G77" s="91"/>
-      <c r="H77" s="91"/>
-    </row>
-    <row r="78" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B78" s="55" t="s">
+      <c r="C79" s="93" t="n">
+        <f aca="false">C73</f>
+        <v>51000</v>
+      </c>
+      <c r="D79" s="92" t="str">
+        <f aca="false">IF(C79="","",IF('Historical Score'!$C$35=0,"green lines - house book "&amp;'Historical Score'!$C$34,TEXT('Historical Score'!$C$35,"0%")&amp;" of the way to the red lines - house book "&amp;'Historical Score'!$C$34&amp;"; yellows allowed"))</f>
+        <v>green lines - house book Negative</v>
+      </c>
+      <c r="E79" s="92"/>
+      <c r="F79" s="92"/>
+      <c r="G79" s="92"/>
+      <c r="H79" s="92"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="C78" s="90" t="s">
+      <c r="C80" s="94" t="n">
+        <f aca="false">IF(OR(C73="",C73="-"),C73,IF('Historical Score'!$C$34="Negative",FLOOR(C73*(1-Controls!$B$32),500),C73))</f>
+        <v>40500</v>
+      </c>
+      <c r="D80" s="92" t="str">
+        <f aca="false">IF(OR(C80="",C80="-"),"",IF('Historical Score'!$C$34="Negative","C73 cut by "&amp;TEXT(Controls!$B$32,"0%")&amp;" (house book negative)","= max at the sizing line")&amp;IF(B6="","","  |  requested "&amp;TEXT(B6,"$#,##0")))</f>
+        <v>C73 cut by 20% (house book negative)  |  requested $40,000</v>
+      </c>
+      <c r="E80" s="92"/>
+      <c r="F80" s="92"/>
+      <c r="G80" s="92"/>
+      <c r="H80" s="92"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="90" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="95" t="n">
+        <f aca="false">IF(OR(C80="",C80="-"),"",D72)</f>
+        <v>1.45</v>
+      </c>
+      <c r="D81" s="92" t="str">
+        <f aca="false">"from the score band"</f>
+        <v>from the score band</v>
+      </c>
+      <c r="E81" s="92"/>
+      <c r="F81" s="92"/>
+      <c r="G81" s="92"/>
+      <c r="H81" s="92"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="90" t="s">
         <v>105</v>
       </c>
-      <c r="D78" s="91" t="s">
+      <c r="C82" s="96" t="n">
+        <f aca="false">IF(OR(C80="",C80="-"),"",IF($E$6="Weekly",C72/5,C72))</f>
+        <v>25</v>
+      </c>
+      <c r="D82" s="92" t="str">
+        <f aca="false">IF(C82="","",IF($E$6="Weekly","weeks","daily payments")&amp;"  ("&amp;TEXT(C72/$K$9,"0.0")&amp;" months)")</f>
+        <v>weeks  (5.8 months)</v>
+      </c>
+      <c r="E82" s="92"/>
+      <c r="F82" s="92"/>
+      <c r="G82" s="92"/>
+      <c r="H82" s="92"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="C83" s="97" t="n">
+        <f aca="false">IF(OR(C80="",C80="-"),"",IF($E$6="Weekly",C84*5,C84))</f>
+        <v>2349</v>
+      </c>
+      <c r="D83" s="92" t="str">
+        <f aca="false">IF(C83="","","per "&amp;IF($E$6="Weekly","week","business day")&amp;";  monthly "&amp;TEXT(C84*$K$9,"$#,##0")&amp;";  payback "&amp;TEXT(C80*C81,"$#,##0")&amp;";  net "&amp;TEXT(C80*(1-F6),"$#,##0"))</f>
+        <v>per week;  monthly $10,174;  payback $58,725;  net $38,475</v>
+      </c>
+      <c r="E83" s="92"/>
+      <c r="F83" s="92"/>
+      <c r="G83" s="92"/>
+      <c r="H83" s="92"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="90" t="s">
         <v>106</v>
       </c>
-      <c r="E78" s="91"/>
-      <c r="F78" s="91"/>
-      <c r="G78" s="91"/>
-      <c r="H78" s="91"/>
-    </row>
-    <row r="79" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B79" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="90" t="s">
+      <c r="C84" s="97" t="n">
+        <f aca="false">IF(OR(C80="",C80="-"),"",C80*C81/C72)</f>
+        <v>469.8</v>
+      </c>
+      <c r="D84" s="92" t="str">
+        <f aca="false">IF(C84="","","vs max daily at the sizing line "&amp;TEXT(C70,"$#,##0.00"))</f>
+        <v>vs max daily at the sizing line $594.87</v>
+      </c>
+      <c r="E84" s="92"/>
+      <c r="F84" s="92"/>
+      <c r="G84" s="92"/>
+      <c r="H84" s="92"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="90" t="s">
         <v>107</v>
       </c>
-      <c r="D79" s="91" t="s">
+      <c r="C85" s="98" t="n">
+        <f aca="false">IF(C84="","",C84*$K$9/C24)</f>
+        <v>0.117953843478261</v>
+      </c>
+      <c r="D85" s="99" t="str">
+        <f aca="false">IF(C85="","",IF(C85&gt;=G39,"KNOCKOUT",IF(C85&lt;=D39,"GREEN",IF(C85&gt;=E39,"RED","YELLOW"))))</f>
+        <v>GREEN</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="90" t="s">
         <v>108</v>
       </c>
-      <c r="E79" s="91"/>
-      <c r="F79" s="91"/>
-      <c r="G79" s="91"/>
-      <c r="H79" s="91"/>
-    </row>
-    <row r="80" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B80" s="55" t="s">
+      <c r="C86" s="98" t="n">
+        <f aca="false">IF(C84="","",(E34+C84)*$K$9/C24)</f>
+        <v>0.26859732173913</v>
+      </c>
+      <c r="D86" s="100" t="str">
+        <f aca="false">IF(C86="","",IF(C86&gt;=G38,"KNOCKOUT",IF(C86&lt;=D38,"GREEN",IF(C86&gt;=E38,"RED","YELLOW"))))</f>
+        <v>GREEN</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="90" t="s">
         <v>109</v>
       </c>
-      <c r="C80" s="90" t="s">
+      <c r="C87" s="98" t="n">
+        <f aca="false">IF(OR(C84="",D24=0),"",(E34+C84)/D24)</f>
+        <v>0.148069204152249</v>
+      </c>
+      <c r="D87" s="100" t="str">
+        <f aca="false">IF(C87="","",IF(C87&gt;=G40,"KNOCKOUT",IF(C87&lt;=D40,"GREEN",IF(C87&gt;=E40,"RED","YELLOW"))))</f>
+        <v>GREEN</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="90" t="s">
         <v>110</v>
       </c>
-      <c r="D80" s="91" t="s">
+      <c r="C88" s="95" t="n">
+        <f aca="false">IF(OR(C80="",C80="-"),"",C80/C24)</f>
+        <v>0.469565217391304</v>
+      </c>
+      <c r="D88" s="100" t="str">
+        <f aca="false">IF(C88="","",IF(C88&gt;=G41,"KNOCKOUT",IF(C88&lt;=D41,"GREEN",IF(C88&gt;=E41,"RED","YELLOW"))))</f>
+        <v>GREEN</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="90" t="s">
         <v>111</v>
       </c>
-      <c r="E80" s="91"/>
-      <c r="F80" s="91"/>
-      <c r="G80" s="91"/>
-      <c r="H80" s="91"/>
-    </row>
-    <row r="81" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B81" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="C81" s="90" t="s">
+      <c r="C89" s="100" t="str">
+        <f aca="false">'Historical Score'!$C$34</f>
+        <v>Negative</v>
+      </c>
+      <c r="D89" s="101" t="str">
+        <f aca="false">'Historical Score'!$C$29&amp;": "&amp;'Historical Score'!$C$30&amp;" seasoned deals, PLR "&amp;IF('Historical Score'!$C$31="","n/a",TEXT('Historical Score'!$C$31,"0.0%"))&amp;" vs book "&amp;TEXT('Historical Score'!$C$10,"0.0%")&amp;", ROF "&amp;IF('Historical Score'!$C$32="","n/a",TEXT('Historical Score'!$C$32,"0.0%"))&amp;", index "&amp;IF('Historical Score'!$C$33="","n/a",TEXT('Historical Score'!$C$33,"0.00"))</f>
+        <v>New/renewal only: 5 seasoned deals, PLR 50.8% vs book 41.0%, ROF -38.3%, index 1.24</v>
+      </c>
+      <c r="E89" s="101"/>
+      <c r="F89" s="101"/>
+      <c r="G89" s="101"/>
+      <c r="H89" s="101"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="102" t="s">
         <v>112</v>
       </c>
-      <c r="D81" s="91" t="s">
-        <v>113</v>
-      </c>
-      <c r="E81" s="91"/>
-      <c r="F81" s="91"/>
-      <c r="G81" s="91"/>
-      <c r="H81" s="91"/>
-    </row>
-    <row r="82" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B82" s="55" t="s">
-        <v>114</v>
-      </c>
-      <c r="C82" s="90" t="s">
-        <v>115</v>
-      </c>
-      <c r="D82" s="91" t="s">
-        <v>116</v>
-      </c>
-      <c r="E82" s="91"/>
-      <c r="F82" s="91"/>
-      <c r="G82" s="91"/>
-      <c r="H82" s="91"/>
-    </row>
-    <row r="83" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B83" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="C83" s="90" t="s">
-        <v>115</v>
-      </c>
-      <c r="D83" s="91" t="s">
-        <v>118</v>
-      </c>
-      <c r="E83" s="91"/>
-      <c r="F83" s="91"/>
-      <c r="G83" s="91"/>
-      <c r="H83" s="91"/>
-    </row>
-    <row r="84" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B84" s="55" t="s">
-        <v>119</v>
-      </c>
-      <c r="C84" s="90" t="s">
-        <v>120</v>
-      </c>
-      <c r="D84" s="91" t="s">
-        <v>121</v>
-      </c>
-      <c r="E84" s="91"/>
-      <c r="F84" s="91"/>
-      <c r="G84" s="91"/>
-      <c r="H84" s="91"/>
-    </row>
-    <row r="85" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B85" s="55" t="s">
-        <v>122</v>
-      </c>
-      <c r="C85" s="90" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" s="91" t="s">
-        <v>124</v>
-      </c>
-      <c r="E85" s="91"/>
-      <c r="F85" s="91"/>
-      <c r="G85" s="91"/>
-      <c r="H85" s="91"/>
-    </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B86" s="92" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -5544,7 +5625,7 @@
     <mergeCell ref="D82:H82"/>
     <mergeCell ref="D83:H83"/>
     <mergeCell ref="D84:H84"/>
-    <mergeCell ref="D85:H85"/>
+    <mergeCell ref="D89:H89"/>
   </mergeCells>
   <conditionalFormatting sqref="F38:F45">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -5600,6 +5681,31 @@
     </cfRule>
     <cfRule type="cellIs" priority="17" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>"MANUAL REVIEW"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D85:D88">
+    <cfRule type="cellIs" priority="18" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>"GREEN"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="19" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>"YELLOW"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="20" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>"RED"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="21" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>"KNOCKOUT"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="cellIs" priority="22" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>"APPROVE"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="23" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>"CONDITIONAL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="24" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>"DECLINE"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -5658,71 +5764,71 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="93" t="s">
-        <v>126</v>
+      <c r="A1" s="103" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="92"/>
+      <c r="A2" s="104"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="95" t="str">
+      <c r="C5" s="96" t="str">
         <f aca="false">IF(Deal!$K$14="","",Deal!$K$14)</f>
         <v>New Deal</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="94" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="95" t="n">
+      <c r="B6" s="105" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="96" t="n">
         <f aca="false">IF(Deal!$C$42="","",Deal!$C$42)</f>
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="95" t="str">
+      <c r="C7" s="96" t="str">
         <f aca="false">IF(Deal!$K$13="","",Deal!$K$13)</f>
         <v>Eating &amp; Drinking Places</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="96" t="str">
+      <c r="C8" s="100" t="str">
         <f aca="false">IF(Deal!$K$12="","",Deal!$K$12)</f>
         <v>Fundwell</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="94" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="97" t="n">
+      <c r="B10" s="105" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="98" t="n">
         <f aca="false">IF($F$20="",0,$F$20)</f>
         <v>0.41</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="94" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="97" t="n">
+      <c r="B11" s="105" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="98" t="n">
         <f aca="false">IF($G$20="",0,$G$20)</f>
         <v>-0.243333333333333</v>
       </c>
@@ -5734,13 +5840,13 @@
         <v>74</v>
       </c>
       <c r="C13" s="89" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="D13" s="89" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E13" s="89" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="F13" s="89" t="s">
         <v>75</v>
@@ -5749,217 +5855,217 @@
         <v>79</v>
       </c>
       <c r="H13" s="89" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I13" s="89"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="55"/>
-      <c r="B14" s="94" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="98" t="n">
+      <c r="B14" s="105" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AU$2:$AU$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>0</v>
       </c>
-      <c r="D14" s="99" t="n">
+      <c r="D14" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AU$2:$AU$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="96" t="str">
+      <c r="E14" s="100" t="str">
         <f aca="false">IF(AND(C14&gt;=Controls!$B$24,D14&gt;=Controls!$B$25),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F14" s="100" t="str">
+      <c r="F14" s="108" t="str">
         <f aca="false">IF(D14=0,"",SUMPRODUCT('Historical Data'!$AU$2:$AU$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D14)</f>
         <v/>
       </c>
-      <c r="G14" s="100" t="str">
+      <c r="G14" s="108" t="str">
         <f aca="false">IF(D14=0,"",SUMPRODUCT('Historical Data'!$AU$2:$AU$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D14)</f>
         <v/>
       </c>
-      <c r="H14" s="101" t="str">
+      <c r="H14" s="109" t="str">
         <f aca="false">IF(OR(F14="",$C$10=0),"",F14/$C$10)</f>
         <v/>
       </c>
-      <c r="I14" s="92"/>
+      <c r="I14" s="104"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="55"/>
-      <c r="B15" s="94" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="98" t="n">
+      <c r="B15" s="105" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AV$2:$AV$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="99" t="n">
+      <c r="D15" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AV$2:$AV$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="96" t="str">
+      <c r="E15" s="100" t="str">
         <f aca="false">IF(AND(C15&gt;=Controls!$B$24,D15&gt;=Controls!$B$25),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F15" s="100" t="str">
+      <c r="F15" s="108" t="str">
         <f aca="false">IF(D15=0,"",SUMPRODUCT('Historical Data'!$AV$2:$AV$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D15)</f>
         <v/>
       </c>
-      <c r="G15" s="100" t="str">
+      <c r="G15" s="108" t="str">
         <f aca="false">IF(D15=0,"",SUMPRODUCT('Historical Data'!$AV$2:$AV$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D15)</f>
         <v/>
       </c>
-      <c r="H15" s="101" t="str">
+      <c r="H15" s="109" t="str">
         <f aca="false">IF(OR(F15="",$C$10=0),"",F15/$C$10)</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="55"/>
-      <c r="B16" s="94" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="98" t="n">
+      <c r="B16" s="105" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AW$2:$AW$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>1</v>
       </c>
-      <c r="D16" s="99" t="n">
+      <c r="D16" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AW$2:$AW$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>10000</v>
       </c>
-      <c r="E16" s="96" t="str">
+      <c r="E16" s="100" t="str">
         <f aca="false">IF(AND(C16&gt;=Controls!$B$24,D16&gt;=Controls!$B$25),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F16" s="100" t="n">
+      <c r="F16" s="108" t="n">
         <f aca="false">IF(D16=0,"",SUMPRODUCT('Historical Data'!$AW$2:$AW$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="100" t="n">
+      <c r="G16" s="108" t="n">
         <f aca="false">IF(D16=0,"",SUMPRODUCT('Historical Data'!$AW$2:$AW$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D16)</f>
         <v>0.5</v>
       </c>
-      <c r="H16" s="101" t="n">
+      <c r="H16" s="109" t="n">
         <f aca="false">IF(OR(F16="",$C$10=0),"",F16/$C$10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="55"/>
-      <c r="B17" s="94" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="98" t="n">
+      <c r="B17" s="105" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AX$2:$AX$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>2</v>
       </c>
-      <c r="D17" s="99" t="n">
+      <c r="D17" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AX$2:$AX$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>40000</v>
       </c>
-      <c r="E17" s="96" t="str">
+      <c r="E17" s="100" t="str">
         <f aca="false">IF(AND(C17&gt;=Controls!$B$24,D17&gt;=Controls!$B$25),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F17" s="100" t="n">
+      <c r="F17" s="108" t="n">
         <f aca="false">IF(D17=0,"",SUMPRODUCT('Historical Data'!$AX$2:$AX$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D17)</f>
         <v>0.525</v>
       </c>
-      <c r="G17" s="100" t="n">
+      <c r="G17" s="108" t="n">
         <f aca="false">IF(D17=0,"",SUMPRODUCT('Historical Data'!$AX$2:$AX$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D17)</f>
         <v>-0.4</v>
       </c>
-      <c r="H17" s="101" t="n">
+      <c r="H17" s="109" t="n">
         <f aca="false">IF(OR(F17="",$C$10=0),"",F17/$C$10)</f>
         <v>1.28048780487805</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="55"/>
-      <c r="B18" s="94" t="s">
-        <v>139</v>
-      </c>
-      <c r="C18" s="98" t="n">
+      <c r="B18" s="105" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AY$2:$AY$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="99" t="n">
+      <c r="D18" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AY$2:$AY$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="96" t="str">
+      <c r="E18" s="100" t="str">
         <f aca="false">IF(AND(C18&gt;=Controls!$B$24,D18&gt;=Controls!$B$25),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F18" s="100" t="str">
+      <c r="F18" s="108" t="str">
         <f aca="false">IF(D18=0,"",SUMPRODUCT('Historical Data'!$AY$2:$AY$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D18)</f>
         <v/>
       </c>
-      <c r="G18" s="100" t="str">
+      <c r="G18" s="108" t="str">
         <f aca="false">IF(D18=0,"",SUMPRODUCT('Historical Data'!$AY$2:$AY$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D18)</f>
         <v/>
       </c>
-      <c r="H18" s="101" t="str">
+      <c r="H18" s="109" t="str">
         <f aca="false">IF(OR(F18="",$C$10=0),"",F18/$C$10)</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="55"/>
-      <c r="B19" s="94" t="s">
-        <v>140</v>
-      </c>
-      <c r="C19" s="98" t="n">
+      <c r="B19" s="105" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AZ$2:$AZ$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>5</v>
       </c>
-      <c r="D19" s="99" t="n">
+      <c r="D19" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AZ$2:$AZ$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>120000</v>
       </c>
-      <c r="E19" s="96" t="str">
+      <c r="E19" s="100" t="str">
         <f aca="false">IF(AND(C19&gt;=Controls!$B$24,D19&gt;=Controls!$B$25),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="F19" s="100" t="n">
+      <c r="F19" s="108" t="n">
         <f aca="false">IF(D19=0,"",SUMPRODUCT('Historical Data'!$AZ$2:$AZ$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D19)</f>
         <v>0.508333333333333</v>
       </c>
-      <c r="G19" s="100" t="n">
+      <c r="G19" s="108" t="n">
         <f aca="false">IF(D19=0,"",SUMPRODUCT('Historical Data'!$AZ$2:$AZ$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D19)</f>
         <v>-0.383333333333333</v>
       </c>
-      <c r="H19" s="101" t="n">
+      <c r="H19" s="109" t="n">
         <f aca="false">IF(OR(F19="",$C$10=0),"",F19/$C$10)</f>
         <v>1.23983739837398</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="55"/>
-      <c r="B20" s="94" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="98" t="n">
+      <c r="B20" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$BA$2:$BA$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>7</v>
       </c>
-      <c r="D20" s="99" t="n">
+      <c r="D20" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$BA$2:$BA$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>150000</v>
       </c>
-      <c r="E20" s="96" t="str">
+      <c r="E20" s="100" t="str">
         <f aca="false">IF(AND(C20&gt;=Controls!$B$24,D20&gt;=Controls!$B$25),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="F20" s="100" t="n">
+      <c r="F20" s="108" t="n">
         <f aca="false">IF(D20=0,"",SUMPRODUCT('Historical Data'!$BA$2:$BA$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D20)</f>
         <v>0.41</v>
       </c>
-      <c r="G20" s="100" t="n">
+      <c r="G20" s="108" t="n">
         <f aca="false">IF(D20=0,"",SUMPRODUCT('Historical Data'!$BA$2:$BA$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D20)</f>
         <v>-0.243333333333333</v>
       </c>
-      <c r="H20" s="101" t="n">
+      <c r="H20" s="109" t="n">
         <f aca="false">IF(OR(F20="",$C$10=0),"",F20/$C$10)</f>
         <v>1</v>
       </c>
@@ -5967,7 +6073,7 @@
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="89"/>
       <c r="B21" s="89" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C21" s="89"/>
       <c r="D21" s="89"/>
@@ -5976,141 +6082,141 @@
       <c r="G21" s="89"/>
       <c r="H21" s="89"/>
       <c r="I21" s="89" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="55"/>
-      <c r="B22" s="94" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" s="98" t="n">
+      <c r="B22" s="105" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AQ$2:$AQ$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>2</v>
       </c>
-      <c r="D22" s="99" t="n">
+      <c r="D22" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AQ$2:$AQ$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>30000</v>
       </c>
-      <c r="E22" s="96" t="str">
+      <c r="E22" s="100" t="str">
         <f aca="false">IF(AND(C22&gt;=Controls!$B$24,D22&gt;=Controls!$B$25),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F22" s="100" t="n">
+      <c r="F22" s="108" t="n">
         <f aca="false">IF(D22=0,"",SUMPRODUCT('Historical Data'!$AQ$2:$AQ$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D22)</f>
         <v>0.0166666666666667</v>
       </c>
-      <c r="G22" s="100" t="n">
+      <c r="G22" s="108" t="n">
         <f aca="false">IF(D22=0,"",SUMPRODUCT('Historical Data'!$AQ$2:$AQ$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D22)</f>
         <v>0.316666666666667</v>
       </c>
-      <c r="H22" s="101" t="n">
+      <c r="H22" s="109" t="n">
         <f aca="false">IF(OR(F22="",$C$10=0),"",F22/$C$10)</f>
         <v>0.040650406504065</v>
       </c>
-      <c r="I22" s="102" t="n">
+      <c r="I22" s="110" t="n">
         <f aca="false">IF(F22="",0,ABS(F22-$C$10))</f>
         <v>0.393333333333333</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="55"/>
-      <c r="B23" s="94" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" s="98" t="n">
+      <c r="B23" s="105" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AR$2:$AR$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>5</v>
       </c>
-      <c r="D23" s="99" t="n">
+      <c r="D23" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AR$2:$AR$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>120000</v>
       </c>
-      <c r="E23" s="96" t="str">
+      <c r="E23" s="100" t="str">
         <f aca="false">IF(AND(C23&gt;=Controls!$B$24,D23&gt;=Controls!$B$25),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="F23" s="100" t="n">
+      <c r="F23" s="108" t="n">
         <f aca="false">IF(D23=0,"",SUMPRODUCT('Historical Data'!$AR$2:$AR$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D23)</f>
         <v>0.508333333333333</v>
       </c>
-      <c r="G23" s="100" t="n">
+      <c r="G23" s="108" t="n">
         <f aca="false">IF(D23=0,"",SUMPRODUCT('Historical Data'!$AR$2:$AR$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D23)</f>
         <v>-0.383333333333333</v>
       </c>
-      <c r="H23" s="101" t="n">
+      <c r="H23" s="109" t="n">
         <f aca="false">IF(OR(F23="",$C$10=0),"",F23/$C$10)</f>
         <v>1.23983739837398</v>
       </c>
-      <c r="I23" s="102" t="n">
+      <c r="I23" s="110" t="n">
         <f aca="false">IF(F23="",0,ABS(F23-$C$10))</f>
         <v>0.0983333333333333</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="55"/>
-      <c r="B24" s="94" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="98" t="n">
+      <c r="B24" s="105" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AS$2:$AS$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>1</v>
       </c>
-      <c r="D24" s="99" t="n">
+      <c r="D24" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AS$2:$AS$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>10000</v>
       </c>
-      <c r="E24" s="96" t="str">
+      <c r="E24" s="100" t="str">
         <f aca="false">IF(AND(C24&gt;=Controls!$B$24,D24&gt;=Controls!$B$25),"Yes","No")</f>
         <v>No</v>
       </c>
-      <c r="F24" s="100" t="n">
+      <c r="F24" s="108" t="n">
         <f aca="false">IF(D24=0,"",SUMPRODUCT('Historical Data'!$AS$2:$AS$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D24)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="100" t="n">
+      <c r="G24" s="108" t="n">
         <f aca="false">IF(D24=0,"",SUMPRODUCT('Historical Data'!$AS$2:$AS$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D24)</f>
         <v>0.5</v>
       </c>
-      <c r="H24" s="101" t="n">
+      <c r="H24" s="109" t="n">
         <f aca="false">IF(OR(F24="",$C$10=0),"",F24/$C$10)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="102" t="n">
+      <c r="I24" s="110" t="n">
         <f aca="false">IF(F24="",0,ABS(F24-$C$10))</f>
         <v>0.41</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="55"/>
-      <c r="B25" s="94" t="s">
-        <v>146</v>
-      </c>
-      <c r="C25" s="98" t="n">
+      <c r="B25" s="105" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="106" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AT$2:$AT$9*'Historical Data'!$AP$2:$AP$9)</f>
         <v>3</v>
       </c>
-      <c r="D25" s="99" t="n">
+      <c r="D25" s="107" t="n">
         <f aca="false">SUMPRODUCT('Historical Data'!$AT$2:$AT$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$N$2:$N$9)</f>
         <v>50000</v>
       </c>
-      <c r="E25" s="96" t="str">
+      <c r="E25" s="100" t="str">
         <f aca="false">IF(AND(C25&gt;=Controls!$B$24,D25&gt;=Controls!$B$25),"Yes","No")</f>
         <v>Yes</v>
       </c>
-      <c r="F25" s="100" t="n">
+      <c r="F25" s="108" t="n">
         <f aca="false">IF(D25=0,"",SUMPRODUCT('Historical Data'!$AT$2:$AT$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AK$2:$AK$9)/D25)</f>
         <v>0.43</v>
       </c>
-      <c r="G25" s="100" t="n">
+      <c r="G25" s="108" t="n">
         <f aca="false">IF(D25=0,"",SUMPRODUCT('Historical Data'!$AT$2:$AT$9*'Historical Data'!$AP$2:$AP$9*'Historical Data'!$AJ$2:$AJ$9)/D25)</f>
         <v>-0.33</v>
       </c>
-      <c r="H25" s="101" t="n">
+      <c r="H25" s="109" t="n">
         <f aca="false">IF(OR(F25="",$C$10=0),"",F25/$C$10)</f>
         <v>1.04878048780488</v>
       </c>
-      <c r="I25" s="102" t="n">
+      <c r="I25" s="110" t="n">
         <f aca="false">IF(F25="",0,ABS(F25-$C$10))</f>
         <v>0.02</v>
       </c>
@@ -6119,98 +6225,98 @@
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="94" t="s">
-        <v>148</v>
-      </c>
-      <c r="C29" s="103" t="str">
+      <c r="B29" s="105" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="111" t="str">
         <f aca="false">INDEX($B$14:$B$20,$D$29)</f>
         <v>New/renewal only</v>
       </c>
-      <c r="D29" s="104" t="n">
+      <c r="D29" s="112" t="n">
         <f aca="false">IFERROR(MATCH("Yes",$E$14:$E$20,0),7)</f>
         <v>6</v>
       </c>
-      <c r="E29" s="105" t="s">
-        <v>149</v>
+      <c r="E29" s="102" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="94" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" s="103" t="n">
+      <c r="B30" s="105" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="111" t="n">
         <f aca="false">INDEX($C$14:$C$20,$D$29)</f>
         <v>5</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="106" t="n">
+      <c r="C31" s="113" t="n">
         <f aca="false">INDEX($F$14:$F$20,$D$29)</f>
         <v>0.508333333333333</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="94" t="s">
+      <c r="B32" s="105" t="s">
         <v>79</v>
       </c>
-      <c r="C32" s="106" t="n">
+      <c r="C32" s="113" t="n">
         <f aca="false">INDEX($G$14:$G$20,$D$29)</f>
         <v>-0.383333333333333</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="94" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" s="107" t="n">
+      <c r="B33" s="105" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="114" t="n">
         <f aca="false">INDEX($H$14:$H$20,$D$29)</f>
         <v>1.23983739837398</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="94" t="s">
-        <v>152</v>
-      </c>
-      <c r="C34" s="108" t="str">
+      <c r="B34" s="105" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="115" t="str">
         <f aca="false">IF(OR(D29=7,C33=""),"Neutral",IF(C33&lt;=Controls!$B$29,"Supportive",IF(C33&gt;Controls!$B$30,"Negative","Neutral")))</f>
         <v>Negative</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="94" t="s">
-        <v>153</v>
-      </c>
-      <c r="C35" s="109" t="n">
+      <c r="B35" s="105" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="116" t="n">
         <f aca="false">IF(C34="Supportive",Controls!$B$31,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="94" t="s">
-        <v>154</v>
-      </c>
-      <c r="C36" s="109" t="str">
+      <c r="B36" s="105" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="116" t="str">
         <f aca="false">IF(MAX($I$22:$I$25)=0,"none rated",INDEX($B$22:$B$25,MATCH(MAX($I$22:$I$25),$I$22:$I$25,0))&amp;": "&amp;TEXT(INDEX($F$22:$F$25,MATCH(MAX($I$22:$I$25),$I$22:$I$25,0)),"0.0%")&amp;" PLR vs "&amp;TEXT($C$10,"0.0%")&amp;" book")</f>
         <v>Industry only: 0.0% PLR vs 41.0% book</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="13"/>
-      <c r="C37" s="110"/>
+      <c r="C37" s="117"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="92"/>
+      <c r="B39" s="104"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7182,7 +7288,7 @@
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7225,25 +7331,25 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="93" t="s">
-        <v>155</v>
+      <c r="A1" s="103" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="111"/>
+      <c r="A2" s="118"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="89" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B4" s="89" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C4" s="89" t="s">
         <v>58</v>
       </c>
       <c r="D4" s="89" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="E4" s="89" t="s">
         <v>81</v>
@@ -7255,49 +7361,49 @@
         <v>31</v>
       </c>
       <c r="H4" s="89" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="I4" s="89" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="89" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="K4" s="89" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="L4" s="89" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="M4" s="89" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="N4" s="89" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="O4" s="89" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="P4" s="89" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="Q4" s="89" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="R4" s="89" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="S4" s="89" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="T4" s="89" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="U4" s="89" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="V4" s="89" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7313,7 +7419,7 @@
         <f aca="false">'Historical Data'!D2</f>
         <v>Closed</v>
       </c>
-      <c r="D5" s="112" t="n">
+      <c r="D5" s="119" t="n">
         <f aca="false">'Historical Data'!E2</f>
         <v>45672</v>
       </c>
@@ -7333,27 +7439,27 @@
         <f aca="false">'Historical Data'!L2</f>
         <v>New Deal</v>
       </c>
-      <c r="I5" s="113" t="n">
+      <c r="I5" s="120" t="n">
         <f aca="false">'Historical Data'!M2</f>
         <v>1.5</v>
       </c>
-      <c r="J5" s="114" t="n">
+      <c r="J5" s="121" t="n">
         <f aca="false">'Historical Data'!N2</f>
         <v>10000</v>
       </c>
-      <c r="K5" s="114" t="n">
+      <c r="K5" s="121" t="n">
         <f aca="false">'Historical Data'!Q2</f>
         <v>15000</v>
       </c>
-      <c r="L5" s="115" t="n">
+      <c r="L5" s="122" t="n">
         <f aca="false">'Historical Data'!S2</f>
         <v>1</v>
       </c>
-      <c r="M5" s="114" t="n">
+      <c r="M5" s="121" t="n">
         <f aca="false">'Historical Data'!AJ2</f>
         <v>5000</v>
       </c>
-      <c r="N5" s="114" t="n">
+      <c r="N5" s="121" t="n">
         <f aca="false">'Historical Data'!AK2</f>
         <v>0</v>
       </c>
@@ -7403,7 +7509,7 @@
         <f aca="false">'Historical Data'!D3</f>
         <v>Closed</v>
       </c>
-      <c r="D6" s="112" t="n">
+      <c r="D6" s="119" t="n">
         <f aca="false">'Historical Data'!E3</f>
         <v>45698</v>
       </c>
@@ -7423,27 +7529,27 @@
         <f aca="false">'Historical Data'!L3</f>
         <v>Renewal</v>
       </c>
-      <c r="I6" s="113" t="n">
+      <c r="I6" s="120" t="n">
         <f aca="false">'Historical Data'!M3</f>
         <v>1.5</v>
       </c>
-      <c r="J6" s="114" t="n">
+      <c r="J6" s="121" t="n">
         <f aca="false">'Historical Data'!N3</f>
         <v>20000</v>
       </c>
-      <c r="K6" s="114" t="n">
+      <c r="K6" s="121" t="n">
         <f aca="false">'Historical Data'!Q3</f>
         <v>30000</v>
       </c>
-      <c r="L6" s="115" t="n">
+      <c r="L6" s="122" t="n">
         <f aca="false">'Historical Data'!S3</f>
         <v>1</v>
       </c>
-      <c r="M6" s="114" t="n">
+      <c r="M6" s="121" t="n">
         <f aca="false">'Historical Data'!AJ3</f>
         <v>10000</v>
       </c>
-      <c r="N6" s="114" t="n">
+      <c r="N6" s="121" t="n">
         <f aca="false">'Historical Data'!AK3</f>
         <v>0</v>
       </c>
@@ -7493,7 +7599,7 @@
         <f aca="false">'Historical Data'!D4</f>
         <v>Legal</v>
       </c>
-      <c r="D7" s="112" t="n">
+      <c r="D7" s="119" t="n">
         <f aca="false">'Historical Data'!E4</f>
         <v>45721</v>
       </c>
@@ -7513,27 +7619,27 @@
         <f aca="false">'Historical Data'!L4</f>
         <v>New Deal</v>
       </c>
-      <c r="I7" s="113" t="n">
+      <c r="I7" s="120" t="n">
         <f aca="false">'Historical Data'!M4</f>
         <v>1.5</v>
       </c>
-      <c r="J7" s="114" t="n">
+      <c r="J7" s="121" t="n">
         <f aca="false">'Historical Data'!N4</f>
         <v>30000</v>
       </c>
-      <c r="K7" s="114" t="n">
+      <c r="K7" s="121" t="n">
         <f aca="false">'Historical Data'!Q4</f>
         <v>9000</v>
       </c>
-      <c r="L7" s="115" t="n">
+      <c r="L7" s="122" t="n">
         <f aca="false">'Historical Data'!S4</f>
         <v>0.2</v>
       </c>
-      <c r="M7" s="114" t="n">
+      <c r="M7" s="121" t="n">
         <f aca="false">'Historical Data'!AJ4</f>
         <v>-21000</v>
       </c>
-      <c r="N7" s="114" t="n">
+      <c r="N7" s="121" t="n">
         <f aca="false">'Historical Data'!AK4</f>
         <v>21000</v>
       </c>
@@ -7583,7 +7689,7 @@
         <f aca="false">'Historical Data'!D5</f>
         <v>In House Collection</v>
       </c>
-      <c r="D8" s="112" t="n">
+      <c r="D8" s="119" t="n">
         <f aca="false">'Historical Data'!E5</f>
         <v>45768</v>
       </c>
@@ -7603,27 +7709,27 @@
         <f aca="false">'Historical Data'!L5</f>
         <v>New Deal</v>
       </c>
-      <c r="I8" s="113" t="n">
+      <c r="I8" s="120" t="n">
         <f aca="false">'Historical Data'!M5</f>
         <v>1.5</v>
       </c>
-      <c r="J8" s="114" t="n">
+      <c r="J8" s="121" t="n">
         <f aca="false">'Historical Data'!N5</f>
         <v>40000</v>
       </c>
-      <c r="K8" s="114" t="n">
+      <c r="K8" s="121" t="n">
         <f aca="false">'Historical Data'!Q5</f>
         <v>20000</v>
       </c>
-      <c r="L8" s="115" t="n">
+      <c r="L8" s="122" t="n">
         <f aca="false">'Historical Data'!S5</f>
         <v>0.333333333333333</v>
       </c>
-      <c r="M8" s="114" t="n">
+      <c r="M8" s="121" t="n">
         <f aca="false">'Historical Data'!AJ5</f>
         <v>-20000</v>
       </c>
-      <c r="N8" s="114" t="n">
+      <c r="N8" s="121" t="n">
         <f aca="false">'Historical Data'!AK5</f>
         <v>20000</v>
       </c>
@@ -7673,7 +7779,7 @@
         <f aca="false">'Historical Data'!D6</f>
         <v>Written-Off</v>
       </c>
-      <c r="D9" s="112" t="n">
+      <c r="D9" s="119" t="n">
         <f aca="false">'Historical Data'!E6</f>
         <v>45789</v>
       </c>
@@ -7693,27 +7799,27 @@
         <f aca="false">'Historical Data'!L6</f>
         <v>Renewal</v>
       </c>
-      <c r="I9" s="113" t="n">
+      <c r="I9" s="120" t="n">
         <f aca="false">'Historical Data'!M6</f>
         <v>1.5</v>
       </c>
-      <c r="J9" s="114" t="n">
+      <c r="J9" s="121" t="n">
         <f aca="false">'Historical Data'!N6</f>
         <v>10000</v>
       </c>
-      <c r="K9" s="114" t="n">
+      <c r="K9" s="121" t="n">
         <f aca="false">'Historical Data'!Q6</f>
         <v>9500</v>
       </c>
-      <c r="L9" s="115" t="n">
+      <c r="L9" s="122" t="n">
         <f aca="false">'Historical Data'!S6</f>
         <v>0.633333333333333</v>
       </c>
-      <c r="M9" s="114" t="n">
+      <c r="M9" s="121" t="n">
         <f aca="false">'Historical Data'!AJ6</f>
         <v>-500</v>
       </c>
-      <c r="N9" s="114" t="n">
+      <c r="N9" s="121" t="n">
         <f aca="false">'Historical Data'!AK6</f>
         <v>500</v>
       </c>
@@ -7763,7 +7869,7 @@
         <f aca="false">'Historical Data'!D7</f>
         <v>Bankruptcy</v>
       </c>
-      <c r="D10" s="112" t="n">
+      <c r="D10" s="119" t="n">
         <f aca="false">'Historical Data'!E7</f>
         <v>45826</v>
       </c>
@@ -7783,27 +7889,27 @@
         <f aca="false">'Historical Data'!L7</f>
         <v>New Deal</v>
       </c>
-      <c r="I10" s="113" t="n">
+      <c r="I10" s="120" t="n">
         <f aca="false">'Historical Data'!M7</f>
         <v>1.5</v>
       </c>
-      <c r="J10" s="114" t="n">
+      <c r="J10" s="121" t="n">
         <f aca="false">'Historical Data'!N7</f>
         <v>20000</v>
       </c>
-      <c r="K10" s="114" t="n">
+      <c r="K10" s="121" t="n">
         <f aca="false">'Historical Data'!Q7</f>
         <v>0</v>
       </c>
-      <c r="L10" s="115" t="n">
+      <c r="L10" s="122" t="n">
         <f aca="false">'Historical Data'!S7</f>
         <v>0</v>
       </c>
-      <c r="M10" s="114" t="n">
+      <c r="M10" s="121" t="n">
         <f aca="false">'Historical Data'!AJ7</f>
         <v>-20000</v>
       </c>
-      <c r="N10" s="114" t="n">
+      <c r="N10" s="121" t="n">
         <f aca="false">'Historical Data'!AK7</f>
         <v>20000</v>
       </c>
@@ -7853,7 +7959,7 @@
         <f aca="false">'Historical Data'!D8</f>
         <v>Open</v>
       </c>
-      <c r="D11" s="112" t="n">
+      <c r="D11" s="119" t="n">
         <f aca="false">'Historical Data'!E8</f>
         <v>46030</v>
       </c>
@@ -7873,27 +7979,27 @@
         <f aca="false">'Historical Data'!L8</f>
         <v>New Deal</v>
       </c>
-      <c r="I11" s="113" t="n">
+      <c r="I11" s="120" t="n">
         <f aca="false">'Historical Data'!M8</f>
         <v>1.5</v>
       </c>
-      <c r="J11" s="114" t="n">
+      <c r="J11" s="121" t="n">
         <f aca="false">'Historical Data'!N8</f>
         <v>50000</v>
       </c>
-      <c r="K11" s="114" t="n">
+      <c r="K11" s="121" t="n">
         <f aca="false">'Historical Data'!Q8</f>
         <v>30000</v>
       </c>
-      <c r="L11" s="115" t="n">
+      <c r="L11" s="122" t="n">
         <f aca="false">'Historical Data'!S8</f>
         <v>0.4</v>
       </c>
-      <c r="M11" s="114" t="n">
+      <c r="M11" s="121" t="n">
         <f aca="false">'Historical Data'!AJ8</f>
         <v>-20000</v>
       </c>
-      <c r="N11" s="114" t="n">
+      <c r="N11" s="121" t="n">
         <f aca="false">'Historical Data'!AK8</f>
         <v>0</v>
       </c>
@@ -7943,7 +8049,7 @@
         <f aca="false">'Historical Data'!D9</f>
         <v>Closed/NSF Unpaid</v>
       </c>
-      <c r="D12" s="112" t="n">
+      <c r="D12" s="119" t="n">
         <f aca="false">'Historical Data'!E9</f>
         <v>45852</v>
       </c>
@@ -7963,27 +8069,27 @@
         <f aca="false">'Historical Data'!L9</f>
         <v>New Deal</v>
       </c>
-      <c r="I12" s="113" t="n">
+      <c r="I12" s="120" t="n">
         <f aca="false">'Historical Data'!M9</f>
         <v>1.5</v>
       </c>
-      <c r="J12" s="114" t="n">
+      <c r="J12" s="121" t="n">
         <f aca="false">'Historical Data'!N9</f>
         <v>20000</v>
       </c>
-      <c r="K12" s="114" t="n">
+      <c r="K12" s="121" t="n">
         <f aca="false">'Historical Data'!Q9</f>
         <v>30000</v>
       </c>
-      <c r="L12" s="115" t="n">
+      <c r="L12" s="122" t="n">
         <f aca="false">'Historical Data'!S9</f>
         <v>1</v>
       </c>
-      <c r="M12" s="114" t="n">
+      <c r="M12" s="121" t="n">
         <f aca="false">'Historical Data'!AJ9</f>
         <v>10000</v>
       </c>
-      <c r="N12" s="114" t="n">
+      <c r="N12" s="121" t="n">
         <f aca="false">'Historical Data'!AK9</f>
         <v>0</v>
       </c>
@@ -9039,249 +9145,249 @@
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="89" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="B1" s="89" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C1" s="89" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D1" s="89" t="s">
         <v>58</v>
       </c>
       <c r="E1" s="89" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="F1" s="89" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="G1" s="89" t="s">
         <v>81</v>
       </c>
       <c r="H1" s="89" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="I1" s="89" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="J1" s="89" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="K1" s="89" t="s">
         <v>31</v>
       </c>
       <c r="L1" s="89" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="M1" s="89" t="s">
         <v>5</v>
       </c>
       <c r="N1" s="89" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="O1" s="89" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="P1" s="89" t="s">
         <v>13</v>
       </c>
       <c r="Q1" s="89" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="R1" s="89" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="S1" s="89" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="T1" s="89" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="U1" s="89" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="V1" s="89" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="W1" s="89" t="s">
         <v>19</v>
       </c>
       <c r="X1" s="89" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y1" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" s="123" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA1" s="123" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB1" s="123" t="s">
+        <v>175</v>
+      </c>
+      <c r="AC1" s="123" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD1" s="123" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE1" s="123" t="s">
+        <v>156</v>
+      </c>
+      <c r="AF1" s="123" t="s">
+        <v>177</v>
+      </c>
+      <c r="AG1" s="123" t="s">
+        <v>178</v>
+      </c>
+      <c r="AH1" s="123" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI1" s="123" t="s">
+        <v>179</v>
+      </c>
+      <c r="AJ1" s="123" t="s">
+        <v>150</v>
+      </c>
+      <c r="AK1" s="123" t="s">
+        <v>151</v>
+      </c>
+      <c r="AL1" s="123" t="s">
+        <v>180</v>
+      </c>
+      <c r="AM1" s="123" t="s">
+        <v>181</v>
+      </c>
+      <c r="AN1" s="123" t="s">
+        <v>182</v>
+      </c>
+      <c r="AO1" s="123" t="s">
+        <v>183</v>
+      </c>
+      <c r="AP1" s="123" t="s">
+        <v>184</v>
+      </c>
+      <c r="AQ1" s="123" t="s">
         <v>185</v>
       </c>
-      <c r="Y1" s="116" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z1" s="116" t="s">
+      <c r="AR1" s="123" t="s">
         <v>186</v>
       </c>
-      <c r="AA1" s="116" t="s">
+      <c r="AS1" s="123" t="s">
         <v>187</v>
       </c>
-      <c r="AB1" s="116" t="s">
+      <c r="AT1" s="123" t="s">
         <v>188</v>
       </c>
-      <c r="AC1" s="116" t="s">
-        <v>168</v>
-      </c>
-      <c r="AD1" s="116" t="s">
+      <c r="AU1" s="123" t="s">
         <v>189</v>
       </c>
-      <c r="AE1" s="116" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF1" s="116" t="s">
+      <c r="AV1" s="123" t="s">
         <v>190</v>
       </c>
-      <c r="AG1" s="116" t="s">
+      <c r="AW1" s="123" t="s">
         <v>191</v>
       </c>
-      <c r="AH1" s="116" t="s">
-        <v>170</v>
-      </c>
-      <c r="AI1" s="116" t="s">
+      <c r="AX1" s="123" t="s">
         <v>192</v>
       </c>
-      <c r="AJ1" s="116" t="s">
-        <v>163</v>
-      </c>
-      <c r="AK1" s="116" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL1" s="116" t="s">
+      <c r="AY1" s="123" t="s">
         <v>193</v>
       </c>
-      <c r="AM1" s="116" t="s">
+      <c r="AZ1" s="123" t="s">
         <v>194</v>
       </c>
-      <c r="AN1" s="116" t="s">
+      <c r="BA1" s="123" t="s">
         <v>195</v>
       </c>
-      <c r="AO1" s="116" t="s">
+      <c r="BB1" s="123" t="s">
         <v>196</v>
       </c>
-      <c r="AP1" s="116" t="s">
+      <c r="BC1" s="123" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="124" t="s">
         <v>197</v>
       </c>
-      <c r="AQ1" s="116" t="s">
+      <c r="B2" s="124" t="s">
         <v>198</v>
       </c>
-      <c r="AR1" s="116" t="s">
+      <c r="C2" s="124" t="s">
         <v>199</v>
       </c>
-      <c r="AS1" s="116" t="s">
+      <c r="D2" s="124" t="s">
         <v>200</v>
       </c>
-      <c r="AT1" s="116" t="s">
+      <c r="E2" s="119" t="n">
+        <v>45672</v>
+      </c>
+      <c r="F2" s="119" t="n">
+        <v>45821</v>
+      </c>
+      <c r="G2" s="124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="AU1" s="116" t="s">
+      <c r="I2" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="AV1" s="116" t="s">
+      <c r="J2" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="AW1" s="116" t="s">
-        <v>204</v>
-      </c>
-      <c r="AX1" s="116" t="s">
-        <v>205</v>
-      </c>
-      <c r="AY1" s="116" t="s">
-        <v>206</v>
-      </c>
-      <c r="AZ1" s="116" t="s">
-        <v>207</v>
-      </c>
-      <c r="BA1" s="116" t="s">
-        <v>208</v>
-      </c>
-      <c r="BB1" s="116" t="s">
-        <v>209</v>
-      </c>
-      <c r="BC1" s="116" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="117" t="s">
-        <v>210</v>
-      </c>
-      <c r="B2" s="117" t="s">
-        <v>211</v>
-      </c>
-      <c r="C2" s="117" t="s">
-        <v>212</v>
-      </c>
-      <c r="D2" s="117" t="s">
-        <v>213</v>
-      </c>
-      <c r="E2" s="112" t="n">
-        <v>45672</v>
-      </c>
-      <c r="F2" s="112" t="n">
-        <v>45821</v>
-      </c>
-      <c r="G2" s="117" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="J2" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="K2" s="117" t="s">
+      <c r="K2" s="124" t="s">
         <v>32</v>
       </c>
       <c r="L2" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="117" t="n">
+      <c r="M2" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N2" s="114" t="n">
+      <c r="N2" s="121" t="n">
         <v>10000</v>
       </c>
-      <c r="O2" s="114" t="n">
+      <c r="O2" s="121" t="n">
         <v>1000</v>
       </c>
-      <c r="P2" s="114" t="n">
+      <c r="P2" s="121" t="n">
         <v>15000</v>
       </c>
-      <c r="Q2" s="114" t="n">
+      <c r="Q2" s="121" t="n">
         <v>15000</v>
       </c>
-      <c r="R2" s="114" t="n">
+      <c r="R2" s="121" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="118" t="n">
+      <c r="S2" s="125" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="117" t="n">
+      <c r="T2" s="124" t="n">
         <v>5</v>
       </c>
-      <c r="U2" s="117" t="n">
+      <c r="U2" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="117" t="n">
+      <c r="V2" s="124" t="n">
         <v>50000</v>
       </c>
-      <c r="W2" s="118" t="n">
+      <c r="W2" s="125" t="n">
         <v>0.12</v>
       </c>
-      <c r="X2" s="112" t="n">
+      <c r="X2" s="119" t="n">
         <v>43160</v>
       </c>
-      <c r="Y2" s="117" t="str">
+      <c r="Y2" s="124" t="str">
         <f aca="false">IF(I2="","No SIC",IFERROR(VLOOKUP(I2,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>Eating &amp; Drinking Places</v>
       </c>
-      <c r="Z2" s="117" t="str">
+      <c r="Z2" s="124" t="str">
         <f aca="false">IF(T2="","",IF(T2&lt;12,"Daily","Weekly"))</f>
         <v>Daily</v>
       </c>
@@ -9321,7 +9427,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D2,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ2" s="114" t="n">
+      <c r="AJ2" s="121" t="n">
         <f aca="false">Q2-N2</f>
         <v>5000</v>
       </c>
@@ -9403,83 +9509,83 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="117" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" s="117" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="117" t="s">
-        <v>219</v>
-      </c>
-      <c r="D3" s="117" t="s">
-        <v>213</v>
-      </c>
-      <c r="E3" s="112" t="n">
+      <c r="A3" s="124" t="s">
+        <v>204</v>
+      </c>
+      <c r="B3" s="124" t="s">
+        <v>205</v>
+      </c>
+      <c r="C3" s="124" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="124" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="119" t="n">
         <v>45698</v>
       </c>
-      <c r="F3" s="112" t="n">
+      <c r="F3" s="119" t="n">
         <v>45848</v>
       </c>
-      <c r="G3" s="117" t="n">
+      <c r="G3" s="124" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="38" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="I3" s="38" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="J3" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="K3" s="117" t="s">
-        <v>223</v>
+        <v>209</v>
+      </c>
+      <c r="K3" s="124" t="s">
+        <v>210</v>
       </c>
       <c r="L3" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="M3" s="117" t="n">
+        <v>183</v>
+      </c>
+      <c r="M3" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N3" s="114" t="n">
+      <c r="N3" s="121" t="n">
         <v>20000</v>
       </c>
-      <c r="O3" s="114" t="n">
+      <c r="O3" s="121" t="n">
         <v>2000</v>
       </c>
-      <c r="P3" s="114" t="n">
+      <c r="P3" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="Q3" s="114" t="n">
+      <c r="Q3" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="R3" s="114" t="n">
+      <c r="R3" s="121" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="118" t="n">
+      <c r="S3" s="125" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="117" t="n">
+      <c r="T3" s="124" t="n">
         <v>20</v>
       </c>
-      <c r="U3" s="117" t="n">
+      <c r="U3" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="117" t="n">
+      <c r="V3" s="124" t="n">
         <v>100000</v>
       </c>
-      <c r="W3" s="118" t="n">
+      <c r="W3" s="125" t="n">
         <v>0.09</v>
       </c>
-      <c r="X3" s="112" t="n">
+      <c r="X3" s="119" t="n">
         <v>42170</v>
       </c>
-      <c r="Y3" s="117" t="str">
+      <c r="Y3" s="124" t="str">
         <f aca="false">IF(I3="","No SIC",IFERROR(VLOOKUP(I3,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>Trucking &amp; Warehousing</v>
       </c>
-      <c r="Z3" s="117" t="str">
+      <c r="Z3" s="124" t="str">
         <f aca="false">IF(T3="","",IF(T3&lt;12,"Daily","Weekly"))</f>
         <v>Weekly</v>
       </c>
@@ -9519,7 +9625,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D3,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ3" s="114" t="n">
+      <c r="AJ3" s="121" t="n">
         <f aca="false">Q3-N3</f>
         <v>10000</v>
       </c>
@@ -9601,83 +9707,83 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="117" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="117" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="117" t="s">
-        <v>226</v>
-      </c>
-      <c r="D4" s="117" t="s">
-        <v>227</v>
-      </c>
-      <c r="E4" s="112" t="n">
+      <c r="A4" s="124" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="124" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="124" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="124" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="119" t="n">
         <v>45721</v>
       </c>
-      <c r="F4" s="112" t="n">
+      <c r="F4" s="119" t="n">
         <v>45813</v>
       </c>
-      <c r="G4" s="117" t="n">
+      <c r="G4" s="124" t="n">
         <v>3</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="I4" s="38" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="K4" s="117" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="124" t="s">
         <v>32</v>
       </c>
       <c r="L4" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="117" t="n">
+      <c r="M4" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N4" s="114" t="n">
+      <c r="N4" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="O4" s="114" t="n">
+      <c r="O4" s="121" t="n">
         <v>3000</v>
       </c>
-      <c r="P4" s="114" t="n">
+      <c r="P4" s="121" t="n">
         <v>45000</v>
       </c>
-      <c r="Q4" s="114" t="n">
+      <c r="Q4" s="121" t="n">
         <v>9000</v>
       </c>
-      <c r="R4" s="114" t="n">
+      <c r="R4" s="121" t="n">
         <v>36000</v>
       </c>
-      <c r="S4" s="118" t="n">
+      <c r="S4" s="125" t="n">
         <v>0.2</v>
       </c>
-      <c r="T4" s="117" t="n">
+      <c r="T4" s="124" t="n">
         <v>6</v>
       </c>
-      <c r="U4" s="117" t="n">
+      <c r="U4" s="124" t="n">
         <v>4</v>
       </c>
-      <c r="V4" s="117" t="n">
+      <c r="V4" s="124" t="n">
         <v>60000</v>
       </c>
-      <c r="W4" s="118" t="n">
+      <c r="W4" s="125" t="n">
         <v>0.15</v>
       </c>
-      <c r="X4" s="112" t="n">
+      <c r="X4" s="119" t="n">
         <v>43840</v>
       </c>
-      <c r="Y4" s="117" t="str">
+      <c r="Y4" s="124" t="str">
         <f aca="false">IF(I4="","No SIC",IFERROR(VLOOKUP(I4,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>General Building Contractors</v>
       </c>
-      <c r="Z4" s="117" t="str">
+      <c r="Z4" s="124" t="str">
         <f aca="false">IF(T4="","",IF(T4&lt;12,"Daily","Weekly"))</f>
         <v>Daily</v>
       </c>
@@ -9717,7 +9823,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D4,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ4" s="114" t="n">
+      <c r="AJ4" s="121" t="n">
         <f aca="false">Q4-N4</f>
         <v>-21000</v>
       </c>
@@ -9799,83 +9905,83 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="117" t="s">
-        <v>230</v>
-      </c>
-      <c r="B5" s="117" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" s="117" t="s">
-        <v>232</v>
-      </c>
-      <c r="D5" s="117" t="s">
-        <v>233</v>
-      </c>
-      <c r="E5" s="112" t="n">
+      <c r="A5" s="124" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="124" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="124" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="124" t="s">
+        <v>220</v>
+      </c>
+      <c r="E5" s="119" t="n">
         <v>45768</v>
       </c>
-      <c r="F5" s="112" t="n">
+      <c r="F5" s="119" t="n">
         <v>45889</v>
       </c>
-      <c r="G5" s="117" t="n">
+      <c r="G5" s="124" t="n">
         <v>3</v>
       </c>
       <c r="H5" s="38" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="K5" s="117" t="s">
-        <v>223</v>
+        <v>209</v>
+      </c>
+      <c r="K5" s="124" t="s">
+        <v>210</v>
       </c>
       <c r="L5" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="M5" s="117" t="n">
+      <c r="M5" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N5" s="114" t="n">
+      <c r="N5" s="121" t="n">
         <v>40000</v>
       </c>
-      <c r="O5" s="114" t="n">
+      <c r="O5" s="121" t="n">
         <v>4000</v>
       </c>
-      <c r="P5" s="114" t="n">
+      <c r="P5" s="121" t="n">
         <v>60000</v>
       </c>
-      <c r="Q5" s="114" t="n">
+      <c r="Q5" s="121" t="n">
         <v>20000</v>
       </c>
-      <c r="R5" s="114" t="n">
+      <c r="R5" s="121" t="n">
         <v>40000</v>
       </c>
-      <c r="S5" s="118" t="n">
+      <c r="S5" s="125" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="T5" s="117" t="n">
+      <c r="T5" s="124" t="n">
         <v>24</v>
       </c>
-      <c r="U5" s="117" t="n">
+      <c r="U5" s="124" t="n">
         <v>7</v>
       </c>
-      <c r="V5" s="117" t="n">
+      <c r="V5" s="124" t="n">
         <v>80000</v>
       </c>
-      <c r="W5" s="118" t="n">
+      <c r="W5" s="125" t="n">
         <v>0.11</v>
       </c>
-      <c r="X5" s="112" t="n">
+      <c r="X5" s="119" t="n">
         <v>41182</v>
       </c>
-      <c r="Y5" s="117" t="str">
+      <c r="Y5" s="124" t="str">
         <f aca="false">IF(I5="","No SIC",IFERROR(VLOOKUP(I5,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>Auto Repair &amp; Services</v>
       </c>
-      <c r="Z5" s="117" t="str">
+      <c r="Z5" s="124" t="str">
         <f aca="false">IF(T5="","",IF(T5&lt;12,"Daily","Weekly"))</f>
         <v>Weekly</v>
       </c>
@@ -9915,7 +10021,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D5,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ5" s="114" t="n">
+      <c r="AJ5" s="121" t="n">
         <f aca="false">Q5-N5</f>
         <v>-20000</v>
       </c>
@@ -9997,83 +10103,83 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="117" t="s">
-        <v>236</v>
-      </c>
-      <c r="B6" s="117" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" s="117" t="s">
-        <v>238</v>
-      </c>
-      <c r="D6" s="117" t="s">
-        <v>239</v>
-      </c>
-      <c r="E6" s="112" t="n">
+      <c r="A6" s="124" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="124" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="124" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="124" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="119" t="n">
         <v>45789</v>
       </c>
-      <c r="F6" s="112" t="n">
+      <c r="F6" s="119" t="n">
         <v>45973</v>
       </c>
-      <c r="G6" s="117" t="n">
+      <c r="G6" s="124" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="38" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="I6" s="38" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6" s="117" t="s">
+        <v>203</v>
+      </c>
+      <c r="K6" s="124" t="s">
         <v>32</v>
       </c>
       <c r="L6" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="M6" s="117" t="n">
+        <v>183</v>
+      </c>
+      <c r="M6" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N6" s="114" t="n">
+      <c r="N6" s="121" t="n">
         <v>10000</v>
       </c>
-      <c r="O6" s="114" t="n">
+      <c r="O6" s="121" t="n">
         <v>1000</v>
       </c>
-      <c r="P6" s="114" t="n">
+      <c r="P6" s="121" t="n">
         <v>15000</v>
       </c>
-      <c r="Q6" s="114" t="n">
+      <c r="Q6" s="121" t="n">
         <v>9500</v>
       </c>
-      <c r="R6" s="114" t="n">
+      <c r="R6" s="121" t="n">
         <v>5500</v>
       </c>
-      <c r="S6" s="118" t="n">
+      <c r="S6" s="125" t="n">
         <v>0.633333333333333</v>
       </c>
-      <c r="T6" s="117" t="n">
+      <c r="T6" s="124" t="n">
         <v>4</v>
       </c>
-      <c r="U6" s="117" t="n">
+      <c r="U6" s="124" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="117" t="n">
+      <c r="V6" s="124" t="n">
         <v>20000</v>
       </c>
-      <c r="W6" s="118" t="n">
+      <c r="W6" s="125" t="n">
         <v>0.14</v>
       </c>
-      <c r="X6" s="112" t="n">
+      <c r="X6" s="119" t="n">
         <v>43774</v>
       </c>
-      <c r="Y6" s="117" t="str">
+      <c r="Y6" s="124" t="str">
         <f aca="false">IF(I6="","No SIC",IFERROR(VLOOKUP(I6,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>Personal Services</v>
       </c>
-      <c r="Z6" s="117" t="str">
+      <c r="Z6" s="124" t="str">
         <f aca="false">IF(T6="","",IF(T6&lt;12,"Daily","Weekly"))</f>
         <v>Daily</v>
       </c>
@@ -10113,7 +10219,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D6,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ6" s="114" t="n">
+      <c r="AJ6" s="121" t="n">
         <f aca="false">Q6-N6</f>
         <v>-500</v>
       </c>
@@ -10195,77 +10301,77 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="117" t="s">
-        <v>242</v>
-      </c>
-      <c r="B7" s="117" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" s="117" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" s="117" t="s">
-        <v>245</v>
-      </c>
-      <c r="E7" s="112" t="n">
+      <c r="A7" s="124" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="124" t="s">
+        <v>230</v>
+      </c>
+      <c r="C7" s="124" t="s">
+        <v>231</v>
+      </c>
+      <c r="D7" s="124" t="s">
+        <v>232</v>
+      </c>
+      <c r="E7" s="119" t="n">
         <v>45826</v>
       </c>
-      <c r="F7" s="112" t="n">
+      <c r="F7" s="119" t="n">
         <v>45918</v>
       </c>
-      <c r="G7" s="117" t="n">
+      <c r="G7" s="124" t="n">
         <v>4</v>
       </c>
       <c r="J7" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="K7" s="117" t="s">
-        <v>223</v>
+        <v>209</v>
+      </c>
+      <c r="K7" s="124" t="s">
+        <v>210</v>
       </c>
       <c r="L7" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="117" t="n">
+      <c r="M7" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N7" s="114" t="n">
+      <c r="N7" s="121" t="n">
         <v>20000</v>
       </c>
-      <c r="O7" s="114" t="n">
+      <c r="O7" s="121" t="n">
         <v>2000</v>
       </c>
-      <c r="P7" s="114" t="n">
+      <c r="P7" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="Q7" s="114" t="n">
+      <c r="Q7" s="121" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="114" t="n">
+      <c r="R7" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="S7" s="118" t="n">
+      <c r="S7" s="125" t="n">
         <v>0</v>
       </c>
-      <c r="T7" s="117" t="n">
+      <c r="T7" s="124" t="n">
         <v>16</v>
       </c>
-      <c r="U7" s="117" t="n">
+      <c r="U7" s="124" t="n">
         <v>9</v>
       </c>
-      <c r="V7" s="117" t="n">
+      <c r="V7" s="124" t="n">
         <v>100000</v>
       </c>
-      <c r="W7" s="118" t="n">
+      <c r="W7" s="125" t="n">
         <v>0.1</v>
       </c>
-      <c r="X7" s="112" t="n">
+      <c r="X7" s="119" t="n">
         <v>44305</v>
       </c>
-      <c r="Y7" s="117" t="str">
+      <c r="Y7" s="124" t="str">
         <f aca="false">IF(I7="","No SIC",IFERROR(VLOOKUP(I7,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>No SIC</v>
       </c>
-      <c r="Z7" s="117" t="str">
+      <c r="Z7" s="124" t="str">
         <f aca="false">IF(T7="","",IF(T7&lt;12,"Daily","Weekly"))</f>
         <v>Weekly</v>
       </c>
@@ -10305,7 +10411,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D7,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ7" s="114" t="n">
+      <c r="AJ7" s="121" t="n">
         <f aca="false">Q7-N7</f>
         <v>-20000</v>
       </c>
@@ -10387,83 +10493,83 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="117" t="s">
-        <v>246</v>
-      </c>
-      <c r="B8" s="117" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>248</v>
-      </c>
-      <c r="D8" s="117" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="112" t="n">
+      <c r="A8" s="124" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" s="124" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="124" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="124" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="119" t="n">
         <v>46030</v>
       </c>
-      <c r="F8" s="112" t="n">
+      <c r="F8" s="119" t="n">
         <v>46237</v>
       </c>
-      <c r="G8" s="117" t="n">
+      <c r="G8" s="124" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="38" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="K8" s="117" t="s">
+        <v>203</v>
+      </c>
+      <c r="K8" s="124" t="s">
         <v>32</v>
       </c>
       <c r="L8" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="117" t="n">
+      <c r="M8" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N8" s="114" t="n">
+      <c r="N8" s="121" t="n">
         <v>50000</v>
       </c>
-      <c r="O8" s="114" t="n">
+      <c r="O8" s="121" t="n">
         <v>5000</v>
       </c>
-      <c r="P8" s="114" t="n">
+      <c r="P8" s="121" t="n">
         <v>75000</v>
       </c>
-      <c r="Q8" s="114" t="n">
+      <c r="Q8" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="R8" s="114" t="n">
+      <c r="R8" s="121" t="n">
         <v>45000</v>
       </c>
-      <c r="S8" s="118" t="n">
+      <c r="S8" s="125" t="n">
         <v>0.4</v>
       </c>
-      <c r="T8" s="117" t="n">
+      <c r="T8" s="124" t="n">
         <v>6</v>
       </c>
-      <c r="U8" s="117" t="n">
+      <c r="U8" s="124" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="117" t="n">
+      <c r="V8" s="124" t="n">
         <v>250000</v>
       </c>
-      <c r="W8" s="118" t="n">
+      <c r="W8" s="125" t="n">
         <v>0.08</v>
       </c>
-      <c r="X8" s="112" t="n">
+      <c r="X8" s="119" t="n">
         <v>40211</v>
       </c>
-      <c r="Y8" s="117" t="str">
+      <c r="Y8" s="124" t="str">
         <f aca="false">IF(I8="","No SIC",IFERROR(VLOOKUP(I8,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>Health Services</v>
       </c>
-      <c r="Z8" s="117" t="str">
+      <c r="Z8" s="124" t="str">
         <f aca="false">IF(T8="","",IF(T8&lt;12,"Daily","Weekly"))</f>
         <v>Daily</v>
       </c>
@@ -10503,7 +10609,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D8,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ8" s="114" t="n">
+      <c r="AJ8" s="121" t="n">
         <f aca="false">Q8-N8</f>
         <v>-20000</v>
       </c>
@@ -10585,80 +10691,80 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="117" t="s">
-        <v>251</v>
-      </c>
-      <c r="B9" s="117" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="117" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="117" t="s">
-        <v>254</v>
-      </c>
-      <c r="E9" s="112" t="n">
+      <c r="A9" s="124" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>240</v>
+      </c>
+      <c r="D9" s="124" t="s">
+        <v>241</v>
+      </c>
+      <c r="E9" s="119" t="n">
         <v>45852</v>
       </c>
-      <c r="F9" s="112" t="n">
+      <c r="F9" s="119" t="n">
         <v>46006</v>
       </c>
-      <c r="G9" s="117" t="n">
+      <c r="G9" s="124" t="n">
         <v>3</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="J9" s="38" t="s">
-        <v>222</v>
-      </c>
-      <c r="K9" s="117" t="s">
-        <v>223</v>
+        <v>209</v>
+      </c>
+      <c r="K9" s="124" t="s">
+        <v>210</v>
       </c>
       <c r="L9" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="117" t="n">
+      <c r="M9" s="124" t="n">
         <v>1.5</v>
       </c>
-      <c r="N9" s="114" t="n">
+      <c r="N9" s="121" t="n">
         <v>20000</v>
       </c>
-      <c r="O9" s="114" t="n">
+      <c r="O9" s="121" t="n">
         <v>2000</v>
       </c>
-      <c r="P9" s="114" t="n">
+      <c r="P9" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="Q9" s="114" t="n">
+      <c r="Q9" s="121" t="n">
         <v>30000</v>
       </c>
-      <c r="R9" s="114" t="n">
+      <c r="R9" s="121" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="118" t="n">
+      <c r="S9" s="125" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="117" t="n">
+      <c r="T9" s="124" t="n">
         <v>20</v>
       </c>
-      <c r="U9" s="117" t="n">
+      <c r="U9" s="124" t="n">
         <v>11</v>
       </c>
-      <c r="W9" s="118" t="n">
+      <c r="W9" s="125" t="n">
         <v>0.13</v>
       </c>
-      <c r="X9" s="112" t="n">
+      <c r="X9" s="119" t="n">
         <v>44781</v>
       </c>
-      <c r="Y9" s="117" t="str">
+      <c r="Y9" s="124" t="str">
         <f aca="false">IF(I9="","No SIC",IFERROR(VLOOKUP(I9,Ref!$A$2:$B$65,2,FALSE()),"Unclassified"))</f>
         <v>Business Services</v>
       </c>
-      <c r="Z9" s="117" t="str">
+      <c r="Z9" s="124" t="str">
         <f aca="false">IF(T9="","",IF(T9&lt;12,"Daily","Weekly"))</f>
         <v>Weekly</v>
       </c>
@@ -10698,7 +10804,7 @@
         <f aca="false">IF(ISNUMBER(MATCH(D9,Controls!$A$36:$A$46,0)),1,0)</f>
         <v>1</v>
       </c>
-      <c r="AJ9" s="114" t="n">
+      <c r="AJ9" s="121" t="n">
         <f aca="false">Q9-N9</f>
         <v>10000</v>
       </c>
@@ -11785,16 +11891,16 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="93" t="s">
-        <v>257</v>
+      <c r="A1" s="103" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="92"/>
+      <c r="A2" s="104"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -11802,10 +11908,10 @@
     </row>
     <row r="4" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="89" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="B4" s="89" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="C4" s="89" t="s">
         <v>5</v>
@@ -11815,132 +11921,132 @@
       <c r="F4" s="89"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="119" t="n">
+      <c r="A5" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="120" t="n">
+      <c r="B5" s="127" t="n">
         <v>100</v>
       </c>
-      <c r="C5" s="121" t="n">
+      <c r="C5" s="128" t="n">
         <v>1.49</v>
       </c>
-      <c r="D5" s="122"/>
-      <c r="E5" s="123"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="130"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="119" t="n">
+      <c r="A6" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="120" t="n">
+      <c r="B6" s="127" t="n">
         <v>130</v>
       </c>
-      <c r="C6" s="121" t="n">
+      <c r="C6" s="128" t="n">
         <v>1.45</v>
       </c>
-      <c r="D6" s="122"/>
-      <c r="E6" s="124"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="131"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="119" t="n">
+      <c r="A7" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="120" t="n">
+      <c r="B7" s="127" t="n">
         <v>150</v>
       </c>
-      <c r="C7" s="121" t="n">
+      <c r="C7" s="128" t="n">
         <v>1.45</v>
       </c>
-      <c r="D7" s="122"/>
-      <c r="E7" s="124"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="131"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="119" t="n">
+      <c r="A8" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="120" t="n">
+      <c r="B8" s="127" t="n">
         <v>195</v>
       </c>
-      <c r="C8" s="121" t="n">
+      <c r="C8" s="128" t="n">
         <v>1.4</v>
       </c>
-      <c r="D8" s="121"/>
-      <c r="E8" s="124"/>
+      <c r="D8" s="128"/>
+      <c r="E8" s="131"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="94" t="s">
-        <v>261</v>
-      </c>
-      <c r="B9" s="120" t="n">
+      <c r="A9" s="105" t="s">
+        <v>248</v>
+      </c>
+      <c r="B9" s="127" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="124"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="131"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13"/>
-      <c r="B10" s="122"/>
-      <c r="C10" s="122"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="124"/>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="131"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="125" t="s">
-        <v>262</v>
-      </c>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="124"/>
+      <c r="A11" s="132" t="s">
+        <v>249</v>
+      </c>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="131"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="94" t="s">
-        <v>263</v>
-      </c>
-      <c r="B12" s="126" t="n">
+      <c r="A12" s="105" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="133" t="n">
         <v>4.331</v>
       </c>
-      <c r="C12" s="120"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="124"/>
+      <c r="C12" s="127"/>
+      <c r="D12" s="127"/>
+      <c r="E12" s="131"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="94" t="s">
-        <v>264</v>
-      </c>
-      <c r="B13" s="126" t="n">
+      <c r="A13" s="105" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="133" t="n">
         <v>21.655</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="94" t="s">
-        <v>265</v>
-      </c>
-      <c r="B14" s="120" t="n">
+      <c r="A14" s="105" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" s="127" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="94" t="s">
-        <v>266</v>
-      </c>
-      <c r="B15" s="120" t="n">
+      <c r="A15" s="105" t="s">
+        <v>253</v>
+      </c>
+      <c r="B15" s="127" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="94" t="s">
-        <v>267</v>
-      </c>
-      <c r="B16" s="127" t="n">
+      <c r="A16" s="105" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" s="134" t="n">
         <v>30.4375</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="128" t="s">
-        <v>268</v>
-      </c>
-      <c r="B17" s="121" t="n">
+      <c r="A17" s="135" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="128" t="n">
         <v>1.45</v>
       </c>
     </row>
@@ -11953,73 +12059,73 @@
       <c r="F18" s="89"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="129" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="129"/>
-      <c r="C19" s="129"/>
-      <c r="D19" s="129"/>
+      <c r="A19" s="136" t="s">
+        <v>256</v>
+      </c>
+      <c r="B19" s="136"/>
+      <c r="C19" s="136"/>
+      <c r="D19" s="136"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="130" t="s">
-        <v>270</v>
-      </c>
-      <c r="B20" s="131" t="n">
+      <c r="A20" s="137" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" s="138" t="n">
         <v>46259</v>
       </c>
-      <c r="C20" s="121"/>
+      <c r="C20" s="128"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="130" t="s">
-        <v>271</v>
-      </c>
-      <c r="B21" s="131" t="n">
+      <c r="A21" s="137" t="s">
+        <v>258</v>
+      </c>
+      <c r="B21" s="138" t="n">
         <v>45597</v>
       </c>
-      <c r="C21" s="121"/>
+      <c r="C21" s="128"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="130" t="s">
-        <v>272</v>
-      </c>
-      <c r="B22" s="131" t="n">
+      <c r="A22" s="137" t="s">
+        <v>259</v>
+      </c>
+      <c r="B22" s="138" t="n">
         <v>46259</v>
       </c>
-      <c r="C22" s="121"/>
+      <c r="C22" s="128"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="94" t="s">
-        <v>273</v>
-      </c>
-      <c r="B23" s="121" t="n">
+      <c r="A23" s="105" t="s">
+        <v>260</v>
+      </c>
+      <c r="B23" s="128" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="94" t="s">
-        <v>274</v>
-      </c>
-      <c r="B24" s="120" t="n">
+      <c r="A24" s="105" t="s">
+        <v>261</v>
+      </c>
+      <c r="B24" s="127" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="121"/>
-      <c r="D24" s="121"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="94" t="s">
-        <v>275</v>
-      </c>
-      <c r="B25" s="132" t="n">
+      <c r="A25" s="105" t="s">
+        <v>262</v>
+      </c>
+      <c r="B25" s="139" t="n">
         <v>30000</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
+      <c r="C25" s="126"/>
+      <c r="D25" s="126"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="94" t="s">
-        <v>276</v>
-      </c>
-      <c r="B26" s="120" t="n">
+      <c r="A26" s="105" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" s="127" t="n">
         <v>5</v>
       </c>
     </row>
@@ -12027,52 +12133,52 @@
       <c r="A27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="125" t="s">
-        <v>277</v>
-      </c>
-      <c r="B28" s="125"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
+      <c r="A28" s="132" t="s">
+        <v>264</v>
+      </c>
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="94" t="s">
-        <v>278</v>
-      </c>
-      <c r="B29" s="121" t="n">
+      <c r="A29" s="105" t="s">
+        <v>265</v>
+      </c>
+      <c r="B29" s="128" t="n">
         <v>0.85</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="94" t="s">
-        <v>279</v>
-      </c>
-      <c r="B30" s="121" t="n">
+      <c r="A30" s="105" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30" s="128" t="n">
         <v>1.15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="94" t="s">
-        <v>280</v>
-      </c>
-      <c r="B31" s="133" t="n">
+      <c r="A31" s="105" t="s">
+        <v>267</v>
+      </c>
+      <c r="B31" s="140" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="94" t="s">
-        <v>281</v>
-      </c>
-      <c r="B32" s="133" t="n">
+      <c r="A32" s="105" t="s">
+        <v>268</v>
+      </c>
+      <c r="B32" s="140" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13"/>
-      <c r="B33" s="121"/>
+      <c r="B33" s="128"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -12085,248 +12191,248 @@
         <v>58</v>
       </c>
       <c r="B35" s="89" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C35" s="89" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="D35" s="89" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="E35" s="89" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="F35" s="89" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="94" t="s">
-        <v>213</v>
-      </c>
-      <c r="B36" s="131" t="s">
-        <v>288</v>
-      </c>
-      <c r="C36" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="D36" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="E36" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F36" s="98" t="n">
+      <c r="A36" s="105" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="138" t="s">
+        <v>275</v>
+      </c>
+      <c r="C36" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="D36" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="E36" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F36" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A36)</f>
         <v>2</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="94" t="s">
-        <v>170</v>
-      </c>
-      <c r="B37" s="131" t="s">
-        <v>288</v>
-      </c>
-      <c r="C37" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="D37" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E37" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="F37" s="98" t="n">
+      <c r="A37" s="105" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" s="138" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="D37" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E37" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="F37" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A37)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="94" t="s">
-        <v>227</v>
-      </c>
-      <c r="B38" s="131" t="s">
-        <v>289</v>
-      </c>
-      <c r="C38" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="D38" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E38" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F38" s="98" t="n">
+      <c r="A38" s="105" t="s">
+        <v>214</v>
+      </c>
+      <c r="B38" s="138" t="s">
+        <v>276</v>
+      </c>
+      <c r="C38" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="D38" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E38" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F38" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A38)</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="B39" s="121" t="s">
-        <v>289</v>
-      </c>
-      <c r="C39" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="D39" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E39" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F39" s="98" t="n">
+      <c r="A39" s="105" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" s="128" t="s">
+        <v>276</v>
+      </c>
+      <c r="C39" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="D39" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E39" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F39" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A39)</f>
         <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="94" t="s">
-        <v>290</v>
-      </c>
-      <c r="B40" s="120" t="s">
-        <v>288</v>
-      </c>
-      <c r="C40" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="D40" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E40" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F40" s="98" t="n">
+      <c r="A40" s="105" t="s">
+        <v>277</v>
+      </c>
+      <c r="B40" s="127" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="D40" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E40" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F40" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A40)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="94" t="s">
-        <v>239</v>
-      </c>
-      <c r="B41" s="135" t="s">
-        <v>289</v>
-      </c>
-      <c r="C41" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="D41" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E41" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F41" s="98" t="n">
+      <c r="A41" s="105" t="s">
+        <v>226</v>
+      </c>
+      <c r="B41" s="142" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="D41" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E41" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F41" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A41)</f>
         <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="94" t="s">
-        <v>245</v>
-      </c>
-      <c r="B42" s="120" t="s">
-        <v>289</v>
-      </c>
-      <c r="C42" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="D42" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E42" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F42" s="98" t="n">
+      <c r="A42" s="105" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" s="127" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="D42" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E42" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F42" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A42)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="94" t="s">
-        <v>291</v>
-      </c>
-      <c r="B43" s="120" t="s">
-        <v>289</v>
-      </c>
-      <c r="C43" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="D43" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E43" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F43" s="98" t="n">
+      <c r="A43" s="105" t="s">
+        <v>278</v>
+      </c>
+      <c r="B43" s="127" t="s">
+        <v>276</v>
+      </c>
+      <c r="C43" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="D43" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E43" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F43" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A43)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="94" t="s">
-        <v>292</v>
-      </c>
-      <c r="B44" s="120" t="s">
-        <v>288</v>
-      </c>
-      <c r="C44" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="D44" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="E44" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F44" s="98" t="n">
+      <c r="A44" s="105" t="s">
+        <v>279</v>
+      </c>
+      <c r="B44" s="127" t="s">
+        <v>275</v>
+      </c>
+      <c r="C44" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="D44" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="E44" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F44" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A44)</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="94" t="s">
-        <v>254</v>
-      </c>
-      <c r="B45" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="D45" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="E45" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F45" s="98" t="n">
+      <c r="A45" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="B45" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="C45" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="D45" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="E45" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F45" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A45)</f>
         <v>1</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="94" t="s">
-        <v>293</v>
-      </c>
-      <c r="B46" s="134" t="s">
-        <v>289</v>
-      </c>
-      <c r="C46" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="D46" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="E46" s="134" t="s">
-        <v>288</v>
-      </c>
-      <c r="F46" s="98" t="n">
+      <c r="A46" s="105" t="s">
+        <v>280</v>
+      </c>
+      <c r="B46" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="C46" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="D46" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="E46" s="141" t="s">
+        <v>275</v>
+      </c>
+      <c r="F46" s="106" t="n">
         <f aca="false">COUNTIF('Historical Data'!$D$2:$D$9,A46)</f>
         <v>0</v>
       </c>
@@ -12344,23 +12450,23 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13"/>
-      <c r="B49" s="136"/>
+      <c r="B49" s="143"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="13"/>
-      <c r="B50" s="136"/>
+      <c r="B50" s="143"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="13"/>
-      <c r="B51" s="137"/>
+      <c r="B51" s="144"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13"/>
-      <c r="B52" s="137"/>
+      <c r="B52" s="144"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="92"/>
+      <c r="A54" s="104"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -12377,91 +12483,91 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13"/>
-      <c r="B59" s="134"/>
-      <c r="C59" s="134"/>
-      <c r="D59" s="134"/>
-      <c r="E59" s="134"/>
-      <c r="F59" s="138"/>
+      <c r="B59" s="141"/>
+      <c r="C59" s="141"/>
+      <c r="D59" s="141"/>
+      <c r="E59" s="141"/>
+      <c r="F59" s="145"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13"/>
-      <c r="B60" s="134"/>
-      <c r="C60" s="134"/>
-      <c r="D60" s="134"/>
-      <c r="E60" s="134"/>
-      <c r="F60" s="138"/>
+      <c r="B60" s="141"/>
+      <c r="C60" s="141"/>
+      <c r="D60" s="141"/>
+      <c r="E60" s="141"/>
+      <c r="F60" s="145"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13"/>
-      <c r="B61" s="134"/>
-      <c r="C61" s="134"/>
-      <c r="D61" s="134"/>
-      <c r="E61" s="134"/>
-      <c r="F61" s="138"/>
+      <c r="B61" s="141"/>
+      <c r="C61" s="141"/>
+      <c r="D61" s="141"/>
+      <c r="E61" s="141"/>
+      <c r="F61" s="145"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="13"/>
-      <c r="B62" s="134"/>
-      <c r="C62" s="134"/>
-      <c r="D62" s="134"/>
-      <c r="E62" s="134"/>
-      <c r="F62" s="138"/>
+      <c r="B62" s="141"/>
+      <c r="C62" s="141"/>
+      <c r="D62" s="141"/>
+      <c r="E62" s="141"/>
+      <c r="F62" s="145"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="13"/>
-      <c r="B63" s="134"/>
-      <c r="C63" s="134"/>
-      <c r="D63" s="134"/>
-      <c r="E63" s="134"/>
-      <c r="F63" s="138"/>
+      <c r="B63" s="141"/>
+      <c r="C63" s="141"/>
+      <c r="D63" s="141"/>
+      <c r="E63" s="141"/>
+      <c r="F63" s="145"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="13"/>
-      <c r="B64" s="134"/>
-      <c r="C64" s="134"/>
-      <c r="D64" s="134"/>
-      <c r="E64" s="134"/>
-      <c r="F64" s="138"/>
+      <c r="B64" s="141"/>
+      <c r="C64" s="141"/>
+      <c r="D64" s="141"/>
+      <c r="E64" s="141"/>
+      <c r="F64" s="145"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="13"/>
-      <c r="B65" s="134"/>
-      <c r="C65" s="134"/>
-      <c r="D65" s="134"/>
-      <c r="E65" s="134"/>
-      <c r="F65" s="138"/>
+      <c r="B65" s="141"/>
+      <c r="C65" s="141"/>
+      <c r="D65" s="141"/>
+      <c r="E65" s="141"/>
+      <c r="F65" s="145"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="13"/>
-      <c r="B66" s="134"/>
-      <c r="C66" s="134"/>
-      <c r="D66" s="134"/>
-      <c r="E66" s="134"/>
-      <c r="F66" s="138"/>
+      <c r="B66" s="141"/>
+      <c r="C66" s="141"/>
+      <c r="D66" s="141"/>
+      <c r="E66" s="141"/>
+      <c r="F66" s="145"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13"/>
-      <c r="B67" s="134"/>
-      <c r="C67" s="134"/>
-      <c r="D67" s="134"/>
-      <c r="E67" s="134"/>
-      <c r="F67" s="138"/>
+      <c r="B67" s="141"/>
+      <c r="C67" s="141"/>
+      <c r="D67" s="141"/>
+      <c r="E67" s="141"/>
+      <c r="F67" s="145"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="13"/>
-      <c r="B68" s="134"/>
-      <c r="C68" s="134"/>
-      <c r="D68" s="134"/>
-      <c r="E68" s="134"/>
-      <c r="F68" s="138"/>
+      <c r="B68" s="141"/>
+      <c r="C68" s="141"/>
+      <c r="D68" s="141"/>
+      <c r="E68" s="141"/>
+      <c r="F68" s="145"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13"/>
-      <c r="B69" s="134"/>
-      <c r="C69" s="134"/>
-      <c r="D69" s="134"/>
-      <c r="E69" s="134"/>
-      <c r="F69" s="138"/>
+      <c r="B69" s="141"/>
+      <c r="C69" s="141"/>
+      <c r="D69" s="141"/>
+      <c r="E69" s="141"/>
+      <c r="F69" s="145"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -13438,1735 +13544,1735 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="124" t="s">
+        <v>287</v>
+      </c>
+      <c r="B2" s="124" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="124" t="s">
+        <v>289</v>
+      </c>
+      <c r="E2" s="124" t="s">
+        <v>290</v>
+      </c>
+      <c r="G2" s="124" t="s">
+        <v>291</v>
+      </c>
+      <c r="K2" s="119" t="n">
+        <v>45292</v>
+      </c>
+      <c r="M2" s="124" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="124" t="s">
+        <v>292</v>
+      </c>
+      <c r="B3" s="124" t="s">
+        <v>293</v>
+      </c>
+      <c r="C3" s="124" t="s">
+        <v>289</v>
+      </c>
+      <c r="E3" s="124" t="s">
         <v>294</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="G3" s="124" t="s">
+        <v>288</v>
+      </c>
+      <c r="K3" s="119" t="n">
+        <v>45306</v>
+      </c>
+      <c r="M3" s="124" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="124" t="s">
         <v>295</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="B4" s="124" t="s">
         <v>296</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="C4" s="124" t="s">
+        <v>289</v>
+      </c>
+      <c r="E4" s="124" t="s">
         <v>297</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="G4" s="124" t="s">
+        <v>293</v>
+      </c>
+      <c r="K4" s="119" t="n">
+        <v>45341</v>
+      </c>
+      <c r="M4" s="124" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="124" t="s">
         <v>298</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="B5" s="124" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="117" t="s">
+      <c r="C5" s="124" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="124" t="s">
         <v>300</v>
       </c>
-      <c r="B2" s="117" t="s">
+      <c r="G5" s="124" t="s">
+        <v>296</v>
+      </c>
+      <c r="K5" s="119" t="n">
+        <v>45439</v>
+      </c>
+      <c r="M5" s="124" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="124" t="s">
         <v>301</v>
       </c>
-      <c r="C2" s="117" t="s">
+      <c r="B6" s="124" t="s">
         <v>302</v>
       </c>
-      <c r="E2" s="117" t="s">
+      <c r="C6" s="124" t="s">
         <v>303</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="E6" s="124" t="s">
         <v>304</v>
       </c>
-      <c r="K2" s="112" t="n">
-        <v>45292</v>
-      </c>
-      <c r="M2" s="117" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="117" t="s">
+      <c r="G6" s="124" t="s">
         <v>305</v>
       </c>
-      <c r="B3" s="117" t="s">
+      <c r="K6" s="119" t="n">
+        <v>45462</v>
+      </c>
+      <c r="M6" s="124" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="124" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="B7" s="124" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="124" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="124" t="s">
+        <v>308</v>
+      </c>
+      <c r="G7" s="124" t="s">
+        <v>309</v>
+      </c>
+      <c r="K7" s="119" t="n">
+        <v>45477</v>
+      </c>
+      <c r="M7" s="124" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="124" t="s">
+        <v>216</v>
+      </c>
+      <c r="B8" s="124" t="s">
+        <v>310</v>
+      </c>
+      <c r="C8" s="124" t="s">
+        <v>311</v>
+      </c>
+      <c r="E8" s="124" t="s">
+        <v>312</v>
+      </c>
+      <c r="G8" s="124" t="s">
+        <v>313</v>
+      </c>
+      <c r="K8" s="119" t="n">
+        <v>45537</v>
+      </c>
+      <c r="M8" s="124" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="124" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" s="124" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="124" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" s="124" t="s">
+        <v>316</v>
+      </c>
+      <c r="G9" s="124" t="s">
+        <v>317</v>
+      </c>
+      <c r="K9" s="119" t="n">
+        <v>45579</v>
+      </c>
+      <c r="M9" s="124" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="124" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" s="124" t="s">
+        <v>319</v>
+      </c>
+      <c r="C10" s="124" t="s">
+        <v>311</v>
+      </c>
+      <c r="E10" s="124" t="s">
+        <v>320</v>
+      </c>
+      <c r="G10" s="124" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="119" t="n">
+        <v>45607</v>
+      </c>
+      <c r="M10" s="124" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="124" t="s">
+        <v>322</v>
+      </c>
+      <c r="B11" s="124" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E11" s="124" t="s">
+        <v>325</v>
+      </c>
+      <c r="G11" s="124" t="s">
+        <v>326</v>
+      </c>
+      <c r="K11" s="119" t="n">
+        <v>45624</v>
+      </c>
+      <c r="M11" s="124" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="124" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="124" t="s">
+        <v>317</v>
+      </c>
+      <c r="C12" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" s="124" t="s">
+        <v>328</v>
+      </c>
+      <c r="G12" s="124" t="s">
+        <v>329</v>
+      </c>
+      <c r="K12" s="119" t="n">
+        <v>45651</v>
+      </c>
+      <c r="M12" s="124" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="124" t="s">
+        <v>330</v>
+      </c>
+      <c r="B13" s="124" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="124" t="s">
+        <v>332</v>
+      </c>
+      <c r="G13" s="124" t="s">
+        <v>333</v>
+      </c>
+      <c r="K13" s="119" t="n">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="124" t="s">
+        <v>334</v>
+      </c>
+      <c r="B14" s="124" t="s">
+        <v>335</v>
+      </c>
+      <c r="C14" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E14" s="124" t="s">
+        <v>336</v>
+      </c>
+      <c r="G14" s="124" t="s">
+        <v>337</v>
+      </c>
+      <c r="K14" s="119" t="n">
+        <v>45677</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="124" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="124" t="s">
+        <v>339</v>
+      </c>
+      <c r="C15" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E15" s="124" t="s">
+        <v>340</v>
+      </c>
+      <c r="G15" s="124" t="s">
+        <v>341</v>
+      </c>
+      <c r="K15" s="119" t="n">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="124" t="s">
+        <v>342</v>
+      </c>
+      <c r="B16" s="124" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E16" s="124" t="s">
+        <v>343</v>
+      </c>
+      <c r="G16" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="119" t="n">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="124" t="s">
+        <v>344</v>
+      </c>
+      <c r="B17" s="124" t="s">
+        <v>345</v>
+      </c>
+      <c r="C17" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E17" s="124" t="s">
+        <v>346</v>
+      </c>
+      <c r="G17" s="124" t="s">
+        <v>347</v>
+      </c>
+      <c r="K17" s="119" t="n">
+        <v>45827</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="124" t="s">
+        <v>348</v>
+      </c>
+      <c r="B18" s="124" t="s">
+        <v>349</v>
+      </c>
+      <c r="C18" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E18" s="124" t="s">
+        <v>350</v>
+      </c>
+      <c r="G18" s="124" t="s">
+        <v>351</v>
+      </c>
+      <c r="K18" s="119" t="n">
+        <v>45842</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="124" t="s">
+        <v>352</v>
+      </c>
+      <c r="B19" s="124" t="s">
+        <v>353</v>
+      </c>
+      <c r="C19" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E19" s="124" t="s">
+        <v>354</v>
+      </c>
+      <c r="G19" s="124" t="s">
+        <v>355</v>
+      </c>
+      <c r="K19" s="119" t="n">
+        <v>45901</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="124" t="s">
+        <v>356</v>
+      </c>
+      <c r="B20" s="124" t="s">
+        <v>357</v>
+      </c>
+      <c r="C20" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E20" s="124" t="s">
+        <v>358</v>
+      </c>
+      <c r="G20" s="124" t="s">
+        <v>359</v>
+      </c>
+      <c r="K20" s="119" t="n">
+        <v>45943</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="124" t="s">
+        <v>360</v>
+      </c>
+      <c r="B21" s="124" t="s">
+        <v>361</v>
+      </c>
+      <c r="C21" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E21" s="124" t="s">
+        <v>362</v>
+      </c>
+      <c r="G21" s="124" t="s">
+        <v>363</v>
+      </c>
+      <c r="K21" s="119" t="n">
+        <v>45972</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="124" t="s">
+        <v>364</v>
+      </c>
+      <c r="B22" s="124" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E22" s="124" t="s">
+        <v>365</v>
+      </c>
+      <c r="G22" s="124" t="s">
+        <v>357</v>
+      </c>
+      <c r="K22" s="119" t="n">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="124" t="s">
+        <v>366</v>
+      </c>
+      <c r="B23" s="124" t="s">
+        <v>367</v>
+      </c>
+      <c r="C23" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E23" s="124" t="s">
+        <v>368</v>
+      </c>
+      <c r="G23" s="124" t="s">
+        <v>323</v>
+      </c>
+      <c r="K23" s="119" t="n">
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="124" t="s">
+        <v>369</v>
+      </c>
+      <c r="B24" s="124" t="s">
+        <v>370</v>
+      </c>
+      <c r="C24" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E24" s="124" t="s">
+        <v>371</v>
+      </c>
+      <c r="G24" s="124" t="s">
+        <v>372</v>
+      </c>
+      <c r="K24" s="119" t="n">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="124" t="s">
+        <v>373</v>
+      </c>
+      <c r="B25" s="124" t="s">
+        <v>374</v>
+      </c>
+      <c r="C25" s="124" t="s">
+        <v>324</v>
+      </c>
+      <c r="E25" s="124" t="s">
+        <v>375</v>
+      </c>
+      <c r="G25" s="124" t="s">
+        <v>299</v>
+      </c>
+      <c r="K25" s="119" t="n">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="124" t="s">
+        <v>376</v>
+      </c>
+      <c r="B26" s="124" t="s">
+        <v>377</v>
+      </c>
+      <c r="C26" s="124" t="s">
+        <v>378</v>
+      </c>
+      <c r="E26" s="124" t="s">
+        <v>379</v>
+      </c>
+      <c r="G26" s="124" t="s">
+        <v>335</v>
+      </c>
+      <c r="K26" s="119" t="n">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="124" t="s">
+        <v>208</v>
+      </c>
+      <c r="B27" s="124" t="s">
+        <v>380</v>
+      </c>
+      <c r="C27" s="124" t="s">
+        <v>378</v>
+      </c>
+      <c r="E27" s="124" t="s">
+        <v>381</v>
+      </c>
+      <c r="G27" s="124" t="s">
+        <v>382</v>
+      </c>
+      <c r="K27" s="119" t="n">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="124" t="s">
+        <v>383</v>
+      </c>
+      <c r="B28" s="124" t="s">
+        <v>384</v>
+      </c>
+      <c r="C28" s="124" t="s">
+        <v>378</v>
+      </c>
+      <c r="E28" s="124" t="s">
+        <v>385</v>
+      </c>
+      <c r="G28" s="124" t="s">
+        <v>310</v>
+      </c>
+      <c r="K28" s="119" t="n">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="124" t="s">
+        <v>386</v>
+      </c>
+      <c r="B29" s="124" t="s">
+        <v>305</v>
+      </c>
+      <c r="C29" s="124" t="s">
+        <v>378</v>
+      </c>
+      <c r="E29" s="124" t="s">
+        <v>387</v>
+      </c>
+      <c r="G29" s="124" t="s">
+        <v>388</v>
+      </c>
+      <c r="K29" s="119" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="124" t="s">
+        <v>389</v>
+      </c>
+      <c r="B30" s="124" t="s">
+        <v>390</v>
+      </c>
+      <c r="C30" s="124" t="s">
+        <v>378</v>
+      </c>
+      <c r="E30" s="124" t="s">
+        <v>391</v>
+      </c>
+      <c r="G30" s="124" t="s">
+        <v>392</v>
+      </c>
+      <c r="K30" s="119" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="124" t="s">
+        <v>393</v>
+      </c>
+      <c r="B31" s="124" t="s">
+        <v>341</v>
+      </c>
+      <c r="C31" s="124" t="s">
+        <v>378</v>
+      </c>
+      <c r="E31" s="124" t="s">
+        <v>394</v>
+      </c>
+      <c r="G31" s="124" t="s">
+        <v>315</v>
+      </c>
+      <c r="K31" s="119" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="124" t="s">
+        <v>395</v>
+      </c>
+      <c r="B32" s="124" t="s">
+        <v>351</v>
+      </c>
+      <c r="C32" s="124" t="s">
+        <v>378</v>
+      </c>
+      <c r="E32" s="124" t="s">
+        <v>396</v>
+      </c>
+      <c r="G32" s="124" t="s">
+        <v>397</v>
+      </c>
+      <c r="K32" s="119" t="n">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="124" t="s">
+        <v>398</v>
+      </c>
+      <c r="B33" s="124" t="s">
+        <v>399</v>
+      </c>
+      <c r="C33" s="124" t="s">
+        <v>400</v>
+      </c>
+      <c r="E33" s="124" t="s">
+        <v>401</v>
+      </c>
+      <c r="G33" s="124" t="s">
+        <v>361</v>
+      </c>
+      <c r="K33" s="119" t="n">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="124" t="s">
+        <v>402</v>
+      </c>
+      <c r="B34" s="124" t="s">
+        <v>403</v>
+      </c>
+      <c r="C34" s="124" t="s">
+        <v>400</v>
+      </c>
+      <c r="E34" s="124" t="s">
+        <v>404</v>
+      </c>
+      <c r="G34" s="124" t="s">
+        <v>370</v>
+      </c>
+      <c r="K34" s="119" t="n">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="124" t="s">
+        <v>405</v>
+      </c>
+      <c r="B35" s="124" t="s">
+        <v>329</v>
+      </c>
+      <c r="C35" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E35" s="124" t="s">
+        <v>407</v>
+      </c>
+      <c r="G35" s="124" t="s">
+        <v>408</v>
+      </c>
+      <c r="K35" s="119" t="n">
+        <v>46405</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="124" t="s">
+        <v>409</v>
+      </c>
+      <c r="B36" s="124" t="s">
+        <v>388</v>
+      </c>
+      <c r="C36" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E36" s="124" t="s">
+        <v>410</v>
+      </c>
+      <c r="G36" s="124" t="s">
+        <v>411</v>
+      </c>
+      <c r="K36" s="119" t="n">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="124" t="s">
+        <v>412</v>
+      </c>
+      <c r="B37" s="124" t="s">
+        <v>372</v>
+      </c>
+      <c r="C37" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E37" s="124" t="s">
+        <v>413</v>
+      </c>
+      <c r="G37" s="124" t="s">
+        <v>414</v>
+      </c>
+      <c r="K37" s="119" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="124" t="s">
+        <v>415</v>
+      </c>
+      <c r="B38" s="124" t="s">
+        <v>321</v>
+      </c>
+      <c r="C38" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E38" s="124" t="s">
+        <v>416</v>
+      </c>
+      <c r="G38" s="124" t="s">
+        <v>417</v>
+      </c>
+      <c r="K38" s="119" t="n">
+        <v>46573</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="124" t="s">
+        <v>418</v>
+      </c>
+      <c r="B39" s="124" t="s">
+        <v>313</v>
+      </c>
+      <c r="C39" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E39" s="124" t="s">
+        <v>419</v>
+      </c>
+      <c r="G39" s="124" t="s">
+        <v>377</v>
+      </c>
+      <c r="K39" s="119" t="n">
+        <v>46636</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="124" t="s">
+        <v>420</v>
+      </c>
+      <c r="B40" s="124" t="s">
+        <v>382</v>
+      </c>
+      <c r="C40" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E40" s="124" t="s">
+        <v>421</v>
+      </c>
+      <c r="G40" s="124" t="s">
+        <v>331</v>
+      </c>
+      <c r="K40" s="119" t="n">
+        <v>46671</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="124" t="s">
+        <v>202</v>
+      </c>
+      <c r="B41" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E41" s="124" t="s">
+        <v>422</v>
+      </c>
+      <c r="G41" s="124" t="s">
+        <v>423</v>
+      </c>
+      <c r="K41" s="119" t="n">
+        <v>46702</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="124" t="s">
+        <v>424</v>
+      </c>
+      <c r="B42" s="124" t="s">
+        <v>425</v>
+      </c>
+      <c r="C42" s="124" t="s">
+        <v>406</v>
+      </c>
+      <c r="E42" s="124" t="s">
+        <v>426</v>
+      </c>
+      <c r="G42" s="124" t="s">
+        <v>374</v>
+      </c>
+      <c r="K42" s="119" t="n">
+        <v>46716</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="124" t="s">
+        <v>427</v>
+      </c>
+      <c r="B43" s="124" t="s">
+        <v>428</v>
+      </c>
+      <c r="C43" s="124" t="s">
+        <v>429</v>
+      </c>
+      <c r="E43" s="124" t="s">
+        <v>430</v>
+      </c>
+      <c r="G43" s="124" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="124" t="s">
+        <v>432</v>
+      </c>
+      <c r="B44" s="124" t="s">
+        <v>411</v>
+      </c>
+      <c r="C44" s="124" t="s">
+        <v>429</v>
+      </c>
+      <c r="E44" s="124" t="s">
+        <v>433</v>
+      </c>
+      <c r="G44" s="124" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="124" t="s">
+        <v>434</v>
+      </c>
+      <c r="B45" s="124" t="s">
+        <v>408</v>
+      </c>
+      <c r="C45" s="124" t="s">
+        <v>429</v>
+      </c>
+      <c r="E45" s="124" t="s">
+        <v>435</v>
+      </c>
+      <c r="G45" s="124" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="124" t="s">
+        <v>437</v>
+      </c>
+      <c r="B46" s="124" t="s">
+        <v>438</v>
+      </c>
+      <c r="C46" s="124" t="s">
+        <v>429</v>
+      </c>
+      <c r="E46" s="124" t="s">
+        <v>439</v>
+      </c>
+      <c r="G46" s="124" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="124" t="s">
+        <v>441</v>
+      </c>
+      <c r="B47" s="124" t="s">
+        <v>397</v>
+      </c>
+      <c r="C47" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E47" s="124" t="s">
+        <v>443</v>
+      </c>
+      <c r="G47" s="124" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="124" t="s">
+        <v>228</v>
+      </c>
+      <c r="B48" s="124" t="s">
+        <v>445</v>
+      </c>
+      <c r="C48" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E48" s="124" t="s">
+        <v>446</v>
+      </c>
+      <c r="G48" s="124" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="124" t="s">
+        <v>243</v>
+      </c>
+      <c r="B49" s="124" t="s">
+        <v>333</v>
+      </c>
+      <c r="C49" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E49" s="124" t="s">
+        <v>447</v>
+      </c>
+      <c r="G49" s="124" t="s">
         <v>302</v>
       </c>
-      <c r="E3" s="117" t="s">
-        <v>307</v>
-      </c>
-      <c r="G3" s="117" t="s">
-        <v>301</v>
-      </c>
-      <c r="K3" s="112" t="n">
-        <v>45306</v>
-      </c>
-      <c r="M3" s="117" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="117" t="s">
-        <v>308</v>
-      </c>
-      <c r="B4" s="117" t="s">
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="124" t="s">
+        <v>222</v>
+      </c>
+      <c r="B50" s="124" t="s">
+        <v>326</v>
+      </c>
+      <c r="C50" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E50" s="124" t="s">
+        <v>448</v>
+      </c>
+      <c r="G50" s="124" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="124" t="s">
+        <v>449</v>
+      </c>
+      <c r="B51" s="124" t="s">
+        <v>431</v>
+      </c>
+      <c r="C51" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E51" s="124" t="s">
+        <v>450</v>
+      </c>
+      <c r="G51" s="124" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="124" t="s">
+        <v>451</v>
+      </c>
+      <c r="B52" s="124" t="s">
+        <v>436</v>
+      </c>
+      <c r="C52" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E52" s="124" t="s">
+        <v>452</v>
+      </c>
+      <c r="G52" s="124" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="124" t="s">
+        <v>453</v>
+      </c>
+      <c r="B53" s="124" t="s">
         <v>309</v>
       </c>
-      <c r="C4" s="117" t="s">
-        <v>302</v>
-      </c>
-      <c r="E4" s="117" t="s">
-        <v>310</v>
-      </c>
-      <c r="G4" s="117" t="s">
-        <v>306</v>
-      </c>
-      <c r="K4" s="112" t="n">
-        <v>45341</v>
-      </c>
-      <c r="M4" s="117" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="117" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" s="117" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="117" t="s">
-        <v>302</v>
-      </c>
-      <c r="E5" s="117" t="s">
-        <v>313</v>
-      </c>
-      <c r="G5" s="117" t="s">
-        <v>309</v>
-      </c>
-      <c r="K5" s="112" t="n">
-        <v>45439</v>
-      </c>
-      <c r="M5" s="117" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="117" t="s">
-        <v>314</v>
-      </c>
-      <c r="B6" s="117" t="s">
-        <v>315</v>
-      </c>
-      <c r="C6" s="117" t="s">
-        <v>316</v>
-      </c>
-      <c r="E6" s="117" t="s">
-        <v>317</v>
-      </c>
-      <c r="G6" s="117" t="s">
-        <v>318</v>
-      </c>
-      <c r="K6" s="112" t="n">
-        <v>45462</v>
-      </c>
-      <c r="M6" s="117" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="117" t="s">
+      <c r="C53" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E53" s="124" t="s">
+        <v>454</v>
+      </c>
+      <c r="G53" s="124" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="124" t="s">
+        <v>237</v>
+      </c>
+      <c r="B54" s="124" t="s">
+        <v>392</v>
+      </c>
+      <c r="C54" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E54" s="124" t="s">
+        <v>455</v>
+      </c>
+      <c r="G54" s="124" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="124" t="s">
+        <v>456</v>
+      </c>
+      <c r="B55" s="124" t="s">
+        <v>417</v>
+      </c>
+      <c r="C55" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E55" s="124" t="s">
+        <v>457</v>
+      </c>
+      <c r="G55" s="124" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="124" t="s">
+        <v>458</v>
+      </c>
+      <c r="B56" s="124" t="s">
+        <v>347</v>
+      </c>
+      <c r="C56" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E56" s="124" t="s">
+        <v>459</v>
+      </c>
+      <c r="G56" s="124" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="124" t="s">
+        <v>461</v>
+      </c>
+      <c r="B57" s="124" t="s">
+        <v>462</v>
+      </c>
+      <c r="C57" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E57" s="124" t="s">
+        <v>463</v>
+      </c>
+      <c r="G57" s="124" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="124" t="s">
+        <v>464</v>
+      </c>
+      <c r="B58" s="124" t="s">
+        <v>440</v>
+      </c>
+      <c r="C58" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E58" s="124" t="s">
+        <v>465</v>
+      </c>
+      <c r="G58" s="124" t="s">
         <v>319</v>
       </c>
-      <c r="B7" s="117" t="s">
-        <v>320</v>
-      </c>
-      <c r="C7" s="117" t="s">
-        <v>316</v>
-      </c>
-      <c r="E7" s="117" t="s">
-        <v>321</v>
-      </c>
-      <c r="G7" s="117" t="s">
-        <v>322</v>
-      </c>
-      <c r="K7" s="112" t="n">
-        <v>45477</v>
-      </c>
-      <c r="M7" s="117" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="117" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="117" t="s">
-        <v>323</v>
-      </c>
-      <c r="C8" s="117" t="s">
-        <v>324</v>
-      </c>
-      <c r="E8" s="117" t="s">
-        <v>325</v>
-      </c>
-      <c r="G8" s="117" t="s">
-        <v>326</v>
-      </c>
-      <c r="K8" s="112" t="n">
-        <v>45537</v>
-      </c>
-      <c r="M8" s="117" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="117" t="s">
-        <v>327</v>
-      </c>
-      <c r="B9" s="117" t="s">
-        <v>328</v>
-      </c>
-      <c r="C9" s="117" t="s">
-        <v>324</v>
-      </c>
-      <c r="E9" s="117" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" s="117" t="s">
-        <v>330</v>
-      </c>
-      <c r="K9" s="112" t="n">
-        <v>45579</v>
-      </c>
-      <c r="M9" s="117" t="s">
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="124" t="s">
+        <v>466</v>
+      </c>
+      <c r="B59" s="124" t="s">
+        <v>423</v>
+      </c>
+      <c r="C59" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E59" s="124" t="s">
+        <v>467</v>
+      </c>
+      <c r="G59" s="124" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="124" t="s">
+        <v>468</v>
+      </c>
+      <c r="B60" s="124" t="s">
+        <v>359</v>
+      </c>
+      <c r="C60" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E60" s="124" t="s">
+        <v>469</v>
+      </c>
+      <c r="G60" s="124" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="124" t="s">
+        <v>470</v>
+      </c>
+      <c r="B61" s="124" t="s">
+        <v>460</v>
+      </c>
+      <c r="C61" s="124" t="s">
+        <v>442</v>
+      </c>
+      <c r="E61" s="124" t="s">
+        <v>471</v>
+      </c>
+      <c r="G61" s="124" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="124" t="s">
+        <v>472</v>
+      </c>
+      <c r="B62" s="124" t="s">
+        <v>414</v>
+      </c>
+      <c r="C62" s="124" t="s">
+        <v>473</v>
+      </c>
+      <c r="E62" s="124" t="s">
+        <v>474</v>
+      </c>
+      <c r="G62" s="124" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="124" t="s">
+        <v>475</v>
+      </c>
+      <c r="B63" s="124" t="s">
+        <v>363</v>
+      </c>
+      <c r="C63" s="124" t="s">
+        <v>473</v>
+      </c>
+      <c r="E63" s="124" t="s">
+        <v>476</v>
+      </c>
+      <c r="G63" s="124" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="124" t="s">
+        <v>477</v>
+      </c>
+      <c r="B64" s="124" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="117" t="s">
-        <v>331</v>
-      </c>
-      <c r="B10" s="117" t="s">
-        <v>332</v>
-      </c>
-      <c r="C10" s="117" t="s">
-        <v>324</v>
-      </c>
-      <c r="E10" s="117" t="s">
-        <v>333</v>
-      </c>
-      <c r="G10" s="117" t="s">
-        <v>334</v>
-      </c>
-      <c r="K10" s="112" t="n">
-        <v>45607</v>
-      </c>
-      <c r="M10" s="117" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="117" t="s">
-        <v>335</v>
-      </c>
-      <c r="B11" s="117" t="s">
-        <v>336</v>
-      </c>
-      <c r="C11" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E11" s="117" t="s">
-        <v>338</v>
-      </c>
-      <c r="G11" s="117" t="s">
-        <v>339</v>
-      </c>
-      <c r="K11" s="112" t="n">
-        <v>45624</v>
-      </c>
-      <c r="M11" s="117" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="117" t="s">
-        <v>340</v>
-      </c>
-      <c r="B12" s="117" t="s">
-        <v>330</v>
-      </c>
-      <c r="C12" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E12" s="117" t="s">
-        <v>341</v>
-      </c>
-      <c r="G12" s="117" t="s">
-        <v>342</v>
-      </c>
-      <c r="K12" s="112" t="n">
-        <v>45651</v>
-      </c>
-      <c r="M12" s="117" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="117" t="s">
-        <v>343</v>
-      </c>
-      <c r="B13" s="117" t="s">
-        <v>344</v>
-      </c>
-      <c r="C13" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E13" s="117" t="s">
-        <v>345</v>
-      </c>
-      <c r="G13" s="117" t="s">
-        <v>346</v>
-      </c>
-      <c r="K13" s="112" t="n">
-        <v>45658</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="117" t="s">
-        <v>347</v>
-      </c>
-      <c r="B14" s="117" t="s">
-        <v>348</v>
-      </c>
-      <c r="C14" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E14" s="117" t="s">
-        <v>349</v>
-      </c>
-      <c r="G14" s="117" t="s">
-        <v>350</v>
-      </c>
-      <c r="K14" s="112" t="n">
-        <v>45677</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="117" t="s">
-        <v>351</v>
-      </c>
-      <c r="B15" s="117" t="s">
-        <v>352</v>
-      </c>
-      <c r="C15" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E15" s="117" t="s">
-        <v>353</v>
-      </c>
-      <c r="G15" s="117" t="s">
-        <v>354</v>
-      </c>
-      <c r="K15" s="112" t="n">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="117" t="s">
-        <v>355</v>
-      </c>
-      <c r="B16" s="117" t="s">
-        <v>350</v>
-      </c>
-      <c r="C16" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E16" s="117" t="s">
-        <v>356</v>
-      </c>
-      <c r="G16" s="117" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16" s="112" t="n">
-        <v>45803</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="117" t="s">
-        <v>357</v>
-      </c>
-      <c r="B17" s="117" t="s">
-        <v>358</v>
-      </c>
-      <c r="C17" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E17" s="117" t="s">
-        <v>359</v>
-      </c>
-      <c r="G17" s="117" t="s">
-        <v>360</v>
-      </c>
-      <c r="K17" s="112" t="n">
-        <v>45827</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="117" t="s">
-        <v>361</v>
-      </c>
-      <c r="B18" s="117" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E18" s="117" t="s">
-        <v>363</v>
-      </c>
-      <c r="G18" s="117" t="s">
-        <v>364</v>
-      </c>
-      <c r="K18" s="112" t="n">
-        <v>45842</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="117" t="s">
-        <v>365</v>
-      </c>
-      <c r="B19" s="117" t="s">
-        <v>366</v>
-      </c>
-      <c r="C19" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E19" s="117" t="s">
-        <v>367</v>
-      </c>
-      <c r="G19" s="117" t="s">
-        <v>368</v>
-      </c>
-      <c r="K19" s="112" t="n">
-        <v>45901</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="117" t="s">
-        <v>369</v>
-      </c>
-      <c r="B20" s="117" t="s">
-        <v>370</v>
-      </c>
-      <c r="C20" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E20" s="117" t="s">
-        <v>371</v>
-      </c>
-      <c r="G20" s="117" t="s">
-        <v>372</v>
-      </c>
-      <c r="K20" s="112" t="n">
-        <v>45943</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="117" t="s">
-        <v>373</v>
-      </c>
-      <c r="B21" s="117" t="s">
-        <v>374</v>
-      </c>
-      <c r="C21" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E21" s="117" t="s">
-        <v>375</v>
-      </c>
-      <c r="G21" s="117" t="s">
-        <v>376</v>
-      </c>
-      <c r="K21" s="112" t="n">
-        <v>45972</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="117" t="s">
-        <v>377</v>
-      </c>
-      <c r="B22" s="117" t="s">
-        <v>368</v>
-      </c>
-      <c r="C22" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E22" s="117" t="s">
-        <v>378</v>
-      </c>
-      <c r="G22" s="117" t="s">
-        <v>370</v>
-      </c>
-      <c r="K22" s="112" t="n">
-        <v>45988</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="117" t="s">
-        <v>379</v>
-      </c>
-      <c r="B23" s="117" t="s">
-        <v>380</v>
-      </c>
-      <c r="C23" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E23" s="117" t="s">
-        <v>381</v>
-      </c>
-      <c r="G23" s="117" t="s">
-        <v>336</v>
-      </c>
-      <c r="K23" s="112" t="n">
-        <v>46016</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="117" t="s">
-        <v>382</v>
-      </c>
-      <c r="B24" s="117" t="s">
-        <v>383</v>
-      </c>
-      <c r="C24" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E24" s="117" t="s">
-        <v>384</v>
-      </c>
-      <c r="G24" s="117" t="s">
-        <v>385</v>
-      </c>
-      <c r="K24" s="112" t="n">
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="117" t="s">
-        <v>386</v>
-      </c>
-      <c r="B25" s="117" t="s">
-        <v>387</v>
-      </c>
-      <c r="C25" s="117" t="s">
-        <v>337</v>
-      </c>
-      <c r="E25" s="117" t="s">
-        <v>388</v>
-      </c>
-      <c r="G25" s="117" t="s">
-        <v>312</v>
-      </c>
-      <c r="K25" s="112" t="n">
-        <v>46041</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="117" t="s">
-        <v>389</v>
-      </c>
-      <c r="B26" s="117" t="s">
-        <v>390</v>
-      </c>
-      <c r="C26" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="E26" s="117" t="s">
-        <v>392</v>
-      </c>
-      <c r="G26" s="117" t="s">
-        <v>348</v>
-      </c>
-      <c r="K26" s="112" t="n">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="117" t="s">
-        <v>221</v>
-      </c>
-      <c r="B27" s="117" t="s">
-        <v>393</v>
-      </c>
-      <c r="C27" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="E27" s="117" t="s">
-        <v>394</v>
-      </c>
-      <c r="G27" s="117" t="s">
-        <v>395</v>
-      </c>
-      <c r="K27" s="112" t="n">
-        <v>46167</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="117" t="s">
-        <v>396</v>
-      </c>
-      <c r="B28" s="117" t="s">
-        <v>397</v>
-      </c>
-      <c r="C28" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="E28" s="117" t="s">
-        <v>398</v>
-      </c>
-      <c r="G28" s="117" t="s">
-        <v>323</v>
-      </c>
-      <c r="K28" s="112" t="n">
-        <v>46192</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="117" t="s">
+      <c r="C64" s="124" t="s">
+        <v>473</v>
+      </c>
+      <c r="E64" s="124" t="s">
+        <v>32</v>
+      </c>
+      <c r="G64" s="124" t="s">
         <v>399</v>
       </c>
-      <c r="B29" s="117" t="s">
-        <v>318</v>
-      </c>
-      <c r="C29" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="E29" s="117" t="s">
-        <v>400</v>
-      </c>
-      <c r="G29" s="117" t="s">
-        <v>401</v>
-      </c>
-      <c r="K29" s="112" t="n">
-        <v>46272</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="117" t="s">
-        <v>402</v>
-      </c>
-      <c r="B30" s="117" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="124" t="s">
+        <v>478</v>
+      </c>
+      <c r="B65" s="124" t="s">
+        <v>444</v>
+      </c>
+      <c r="C65" s="124" t="s">
+        <v>473</v>
+      </c>
+      <c r="E65" s="124" t="s">
+        <v>479</v>
+      </c>
+      <c r="G65" s="124" t="s">
         <v>403</v>
       </c>
-      <c r="C30" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="E30" s="117" t="s">
-        <v>404</v>
-      </c>
-      <c r="G30" s="117" t="s">
-        <v>405</v>
-      </c>
-      <c r="K30" s="112" t="n">
-        <v>46307</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="117" t="s">
-        <v>406</v>
-      </c>
-      <c r="B31" s="117" t="s">
-        <v>354</v>
-      </c>
-      <c r="C31" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="E31" s="117" t="s">
-        <v>407</v>
-      </c>
-      <c r="G31" s="117" t="s">
-        <v>328</v>
-      </c>
-      <c r="K31" s="112" t="n">
-        <v>46337</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="117" t="s">
-        <v>408</v>
-      </c>
-      <c r="B32" s="117" t="s">
-        <v>364</v>
-      </c>
-      <c r="C32" s="117" t="s">
-        <v>391</v>
-      </c>
-      <c r="E32" s="117" t="s">
-        <v>409</v>
-      </c>
-      <c r="G32" s="117" t="s">
-        <v>410</v>
-      </c>
-      <c r="K32" s="112" t="n">
-        <v>46352</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="117" t="s">
-        <v>411</v>
-      </c>
-      <c r="B33" s="117" t="s">
-        <v>412</v>
-      </c>
-      <c r="C33" s="117" t="s">
-        <v>413</v>
-      </c>
-      <c r="E33" s="117" t="s">
-        <v>414</v>
-      </c>
-      <c r="G33" s="117" t="s">
-        <v>374</v>
-      </c>
-      <c r="K33" s="112" t="n">
-        <v>46381</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="117" t="s">
-        <v>415</v>
-      </c>
-      <c r="B34" s="117" t="s">
-        <v>416</v>
-      </c>
-      <c r="C34" s="117" t="s">
-        <v>413</v>
-      </c>
-      <c r="E34" s="117" t="s">
-        <v>417</v>
-      </c>
-      <c r="G34" s="117" t="s">
-        <v>383</v>
-      </c>
-      <c r="K34" s="112" t="n">
-        <v>46388</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="117" t="s">
-        <v>418</v>
-      </c>
-      <c r="B35" s="117" t="s">
-        <v>342</v>
-      </c>
-      <c r="C35" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E35" s="117" t="s">
-        <v>420</v>
-      </c>
-      <c r="G35" s="117" t="s">
-        <v>421</v>
-      </c>
-      <c r="K35" s="112" t="n">
-        <v>46405</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="117" t="s">
-        <v>422</v>
-      </c>
-      <c r="B36" s="117" t="s">
-        <v>401</v>
-      </c>
-      <c r="C36" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E36" s="117" t="s">
-        <v>423</v>
-      </c>
-      <c r="G36" s="117" t="s">
-        <v>424</v>
-      </c>
-      <c r="K36" s="112" t="n">
-        <v>46433</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="117" t="s">
-        <v>425</v>
-      </c>
-      <c r="B37" s="117" t="s">
-        <v>385</v>
-      </c>
-      <c r="C37" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E37" s="117" t="s">
-        <v>426</v>
-      </c>
-      <c r="G37" s="117" t="s">
-        <v>427</v>
-      </c>
-      <c r="K37" s="112" t="n">
-        <v>46538</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="117" t="s">
-        <v>428</v>
-      </c>
-      <c r="B38" s="117" t="s">
-        <v>334</v>
-      </c>
-      <c r="C38" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E38" s="117" t="s">
-        <v>429</v>
-      </c>
-      <c r="G38" s="117" t="s">
-        <v>430</v>
-      </c>
-      <c r="K38" s="112" t="n">
-        <v>46573</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="117" t="s">
-        <v>431</v>
-      </c>
-      <c r="B39" s="117" t="s">
-        <v>326</v>
-      </c>
-      <c r="C39" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E39" s="117" t="s">
-        <v>432</v>
-      </c>
-      <c r="G39" s="117" t="s">
-        <v>390</v>
-      </c>
-      <c r="K39" s="112" t="n">
-        <v>46636</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="117" t="s">
-        <v>433</v>
-      </c>
-      <c r="B40" s="117" t="s">
-        <v>395</v>
-      </c>
-      <c r="C40" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E40" s="117" t="s">
-        <v>434</v>
-      </c>
-      <c r="G40" s="117" t="s">
-        <v>344</v>
-      </c>
-      <c r="K40" s="112" t="n">
-        <v>46671</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="117" t="s">
-        <v>215</v>
-      </c>
-      <c r="B41" s="117" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E41" s="117" t="s">
-        <v>435</v>
-      </c>
-      <c r="G41" s="117" t="s">
-        <v>436</v>
-      </c>
-      <c r="K41" s="112" t="n">
-        <v>46702</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="117" t="s">
-        <v>437</v>
-      </c>
-      <c r="B42" s="117" t="s">
-        <v>438</v>
-      </c>
-      <c r="C42" s="117" t="s">
-        <v>419</v>
-      </c>
-      <c r="E42" s="117" t="s">
-        <v>439</v>
-      </c>
-      <c r="G42" s="117" t="s">
-        <v>387</v>
-      </c>
-      <c r="K42" s="112" t="n">
-        <v>46716</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="117" t="s">
-        <v>440</v>
-      </c>
-      <c r="B43" s="117" t="s">
-        <v>441</v>
-      </c>
-      <c r="C43" s="117" t="s">
-        <v>442</v>
-      </c>
-      <c r="E43" s="117" t="s">
-        <v>443</v>
-      </c>
-      <c r="G43" s="117" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="117" t="s">
-        <v>445</v>
-      </c>
-      <c r="B44" s="117" t="s">
-        <v>424</v>
-      </c>
-      <c r="C44" s="117" t="s">
-        <v>442</v>
-      </c>
-      <c r="E44" s="117" t="s">
-        <v>446</v>
-      </c>
-      <c r="G44" s="117" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="117" t="s">
-        <v>447</v>
-      </c>
-      <c r="B45" s="117" t="s">
-        <v>421</v>
-      </c>
-      <c r="C45" s="117" t="s">
-        <v>442</v>
-      </c>
-      <c r="E45" s="117" t="s">
-        <v>448</v>
-      </c>
-      <c r="G45" s="117" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="117" t="s">
-        <v>450</v>
-      </c>
-      <c r="B46" s="117" t="s">
-        <v>451</v>
-      </c>
-      <c r="C46" s="117" t="s">
-        <v>442</v>
-      </c>
-      <c r="E46" s="117" t="s">
-        <v>452</v>
-      </c>
-      <c r="G46" s="117" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="117" t="s">
-        <v>454</v>
-      </c>
-      <c r="B47" s="117" t="s">
-        <v>410</v>
-      </c>
-      <c r="C47" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E47" s="117" t="s">
-        <v>456</v>
-      </c>
-      <c r="G47" s="117" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="117" t="s">
-        <v>241</v>
-      </c>
-      <c r="B48" s="117" t="s">
-        <v>458</v>
-      </c>
-      <c r="C48" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E48" s="117" t="s">
-        <v>459</v>
-      </c>
-      <c r="G48" s="117" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="117" t="s">
-        <v>256</v>
-      </c>
-      <c r="B49" s="117" t="s">
-        <v>346</v>
-      </c>
-      <c r="C49" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E49" s="117" t="s">
-        <v>460</v>
-      </c>
-      <c r="G49" s="117" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="117" t="s">
-        <v>235</v>
-      </c>
-      <c r="B50" s="117" t="s">
-        <v>339</v>
-      </c>
-      <c r="C50" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E50" s="117" t="s">
-        <v>461</v>
-      </c>
-      <c r="G50" s="117" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="117" t="s">
-        <v>462</v>
-      </c>
-      <c r="B51" s="117" t="s">
-        <v>444</v>
-      </c>
-      <c r="C51" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E51" s="117" t="s">
-        <v>463</v>
-      </c>
-      <c r="G51" s="117" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="117" t="s">
-        <v>464</v>
-      </c>
-      <c r="B52" s="117" t="s">
-        <v>449</v>
-      </c>
-      <c r="C52" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E52" s="117" t="s">
-        <v>465</v>
-      </c>
-      <c r="G52" s="117" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="117" t="s">
-        <v>466</v>
-      </c>
-      <c r="B53" s="117" t="s">
-        <v>322</v>
-      </c>
-      <c r="C53" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E53" s="117" t="s">
-        <v>467</v>
-      </c>
-      <c r="G53" s="117" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="117" t="s">
-        <v>250</v>
-      </c>
-      <c r="B54" s="117" t="s">
-        <v>405</v>
-      </c>
-      <c r="C54" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E54" s="117" t="s">
-        <v>468</v>
-      </c>
-      <c r="G54" s="117" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="117" t="s">
-        <v>469</v>
-      </c>
-      <c r="B55" s="117" t="s">
-        <v>430</v>
-      </c>
-      <c r="C55" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E55" s="117" t="s">
-        <v>470</v>
-      </c>
-      <c r="G55" s="117" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="117" t="s">
-        <v>471</v>
-      </c>
-      <c r="B56" s="117" t="s">
-        <v>360</v>
-      </c>
-      <c r="C56" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E56" s="117" t="s">
-        <v>472</v>
-      </c>
-      <c r="G56" s="117" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="117" t="s">
-        <v>474</v>
-      </c>
-      <c r="B57" s="117" t="s">
-        <v>475</v>
-      </c>
-      <c r="C57" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E57" s="117" t="s">
-        <v>476</v>
-      </c>
-      <c r="G57" s="117" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="117" t="s">
-        <v>477</v>
-      </c>
-      <c r="B58" s="117" t="s">
-        <v>453</v>
-      </c>
-      <c r="C58" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E58" s="117" t="s">
-        <v>478</v>
-      </c>
-      <c r="G58" s="117" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="117" t="s">
-        <v>479</v>
-      </c>
-      <c r="B59" s="117" t="s">
-        <v>436</v>
-      </c>
-      <c r="C59" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E59" s="117" t="s">
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E66" s="124" t="s">
         <v>480</v>
       </c>
-      <c r="G59" s="117" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="117" t="s">
+      <c r="G66" s="124" t="s">
         <v>481</v>
       </c>
-      <c r="B60" s="117" t="s">
-        <v>372</v>
-      </c>
-      <c r="C60" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E60" s="117" t="s">
+    </row>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E67" s="124" t="s">
         <v>482</v>
       </c>
-      <c r="G60" s="117" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="117" t="s">
+      <c r="G67" s="124" t="s">
         <v>483</v>
       </c>
-      <c r="B61" s="117" t="s">
-        <v>473</v>
-      </c>
-      <c r="C61" s="117" t="s">
-        <v>455</v>
-      </c>
-      <c r="E61" s="117" t="s">
+    </row>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E68" s="124" t="s">
         <v>484</v>
       </c>
-      <c r="G61" s="117" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="117" t="s">
+    </row>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E69" s="124" t="s">
         <v>485</v>
       </c>
-      <c r="B62" s="117" t="s">
-        <v>427</v>
-      </c>
-      <c r="C62" s="117" t="s">
+    </row>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E70" s="124" t="s">
         <v>486</v>
       </c>
-      <c r="E62" s="117" t="s">
+    </row>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E71" s="124" t="s">
         <v>487</v>
       </c>
-      <c r="G62" s="117" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="117" t="s">
+    </row>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E72" s="124" t="s">
         <v>488</v>
       </c>
-      <c r="B63" s="117" t="s">
-        <v>376</v>
-      </c>
-      <c r="C63" s="117" t="s">
-        <v>486</v>
-      </c>
-      <c r="E63" s="117" t="s">
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E73" s="124" t="s">
         <v>489</v>
       </c>
-      <c r="G63" s="117" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="117" t="s">
+    </row>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E74" s="124" t="s">
         <v>490</v>
       </c>
-      <c r="B64" s="117" t="s">
-        <v>304</v>
-      </c>
-      <c r="C64" s="117" t="s">
-        <v>486</v>
-      </c>
-      <c r="E64" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="G64" s="117" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="117" t="s">
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E75" s="124" t="s">
         <v>491</v>
       </c>
-      <c r="B65" s="117" t="s">
-        <v>457</v>
-      </c>
-      <c r="C65" s="117" t="s">
-        <v>486</v>
-      </c>
-      <c r="E65" s="117" t="s">
+    </row>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E76" s="124" t="s">
         <v>492</v>
       </c>
-      <c r="G65" s="117" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E66" s="117" t="s">
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E77" s="124" t="s">
         <v>493</v>
       </c>
-      <c r="G66" s="117" t="s">
+    </row>
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E78" s="124" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E67" s="117" t="s">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E79" s="124" t="s">
         <v>495</v>
       </c>
-      <c r="G67" s="117" t="s">
+    </row>
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E80" s="124" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E68" s="117" t="s">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E81" s="124" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E69" s="117" t="s">
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E82" s="124" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E70" s="117" t="s">
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E83" s="124" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E71" s="117" t="s">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E84" s="124" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E72" s="117" t="s">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E85" s="124" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E73" s="117" t="s">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E86" s="124" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E74" s="117" t="s">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E87" s="124" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E75" s="117" t="s">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E88" s="124" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E76" s="117" t="s">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E89" s="124" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E77" s="117" t="s">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E90" s="124" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E78" s="117" t="s">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E91" s="124" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E79" s="117" t="s">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E92" s="124" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E80" s="117" t="s">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E93" s="124" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E81" s="117" t="s">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E94" s="124" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E82" s="117" t="s">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E95" s="124" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E83" s="117" t="s">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E96" s="124" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E84" s="117" t="s">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E97" s="124" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E85" s="117" t="s">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E98" s="124" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E86" s="117" t="s">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E99" s="124" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E87" s="117" t="s">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E100" s="124" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E88" s="117" t="s">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E101" s="124" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E89" s="117" t="s">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E102" s="124" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E90" s="117" t="s">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E103" s="124" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E91" s="117" t="s">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E104" s="124" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E92" s="117" t="s">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E105" s="124" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E93" s="117" t="s">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E106" s="124" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E94" s="117" t="s">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E107" s="124" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E95" s="117" t="s">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E108" s="124" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E96" s="117" t="s">
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E109" s="124" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E97" s="117" t="s">
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E110" s="124" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E98" s="117" t="s">
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E111" s="124" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E99" s="117" t="s">
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E112" s="124" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E100" s="117" t="s">
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E113" s="124" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E101" s="117" t="s">
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E114" s="124" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E102" s="117" t="s">
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E115" s="124" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E103" s="117" t="s">
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E116" s="124" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E104" s="117" t="s">
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E117" s="124" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E105" s="117" t="s">
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E118" s="124" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E106" s="117" t="s">
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E119" s="124" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E107" s="117" t="s">
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E120" s="124" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E108" s="117" t="s">
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E121" s="124" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E109" s="117" t="s">
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E122" s="124" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E110" s="117" t="s">
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E123" s="124" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E111" s="117" t="s">
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E124" s="124" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E112" s="117" t="s">
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E125" s="124" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E113" s="117" t="s">
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E126" s="124" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E114" s="117" t="s">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E127" s="124" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E115" s="117" t="s">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E128" s="124" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E116" s="117" t="s">
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E129" s="124" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E117" s="117" t="s">
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E130" s="124" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E118" s="117" t="s">
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E131" s="124" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E119" s="117" t="s">
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E132" s="124" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E120" s="117" t="s">
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E133" s="124" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E121" s="117" t="s">
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E134" s="124" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E122" s="117" t="s">
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E135" s="124" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E123" s="117" t="s">
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E136" s="124" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E124" s="117" t="s">
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E137" s="124" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E125" s="117" t="s">
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E138" s="124" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E126" s="117" t="s">
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E139" s="124" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E127" s="117" t="s">
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E140" s="124" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E128" s="117" t="s">
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E141" s="124" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E129" s="117" t="s">
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E142" s="124" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E130" s="117" t="s">
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E143" s="124" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E131" s="117" t="s">
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E144" s="124" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E132" s="117" t="s">
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E145" s="124" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E133" s="117" t="s">
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E146" s="124" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E134" s="117" t="s">
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E147" s="124" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E135" s="117" t="s">
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E148" s="124" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E136" s="117" t="s">
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E149" s="124" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E137" s="117" t="s">
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E150" s="124" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E138" s="117" t="s">
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E151" s="124" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E139" s="117" t="s">
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E152" s="124" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E140" s="117" t="s">
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E153" s="124" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E141" s="117" t="s">
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E154" s="124" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E155" s="124" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E142" s="117" t="s">
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E156" s="124" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E143" s="117" t="s">
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E157" s="124" t="s">
         <v>572</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E144" s="117" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E145" s="117" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E146" s="117" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E147" s="117" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E148" s="117" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E149" s="117" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E150" s="117" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E151" s="117" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E152" s="117" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E153" s="117" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E154" s="117" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E155" s="117" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E156" s="117" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E157" s="117" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
